--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2651,6 +2651,1369 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130865454</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>468469</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7017487</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>130865266</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>468470</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017481</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130865254</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57861</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>468479</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7017488</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetad grov död gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130865004</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>468518</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7017522</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130865182</v>
+      </c>
+      <c r="B26" t="n">
+        <v>91776</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>468493</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7017468</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130865357</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91796</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>468423</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7017415</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130865432</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>468444</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7017417</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>130865409</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>468505</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7017445</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bearbetade död gran. Gott om spår av födosök i området.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>130865230</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>468478</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7017505</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130864922</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57864</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>468571</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7017501</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bearbetad gran med typiska rand mönster.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130865481</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79221</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>468481</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7017551</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130865014</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58023</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>468521</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7017519</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Kristofer Holmsten</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -2765,10 +2765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865266</v>
+        <v>130865254</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>57861</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,34 +2776,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468470</v>
+        <v>468479</v>
       </c>
       <c r="R23" t="n">
-        <v>7017481</v>
+        <v>7017488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2835,7 +2840,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2845,7 +2850,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetad grov död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2872,10 +2882,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130865254</v>
+        <v>130865266</v>
       </c>
       <c r="B24" t="n">
-        <v>57861</v>
+        <v>91772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2883,39 +2893,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468479</v>
+        <v>468470</v>
       </c>
       <c r="R24" t="n">
-        <v>7017488</v>
+        <v>7017481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,7 +2952,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2957,12 +2962,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetad grov död gran</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -3793,10 +3793,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130865014</v>
+        <v>130865481</v>
       </c>
       <c r="B32" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,43 +3804,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468521</v>
+        <v>468481</v>
       </c>
       <c r="R32" t="n">
-        <v>7017519</v>
+        <v>7017551</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3872,7 +3863,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3882,7 +3873,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3909,10 +3900,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130865481</v>
+        <v>130865014</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3920,34 +3911,43 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468481</v>
+        <v>468521</v>
       </c>
       <c r="R33" t="n">
-        <v>7017551</v>
+        <v>7017519</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030313</v>
+        <v>131030174</v>
       </c>
       <c r="B56" t="n">
-        <v>80349</v>
+        <v>58043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,37 +6552,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468321</v>
+        <v>468273</v>
       </c>
       <c r="R56" t="n">
-        <v>7017305</v>
+        <v>7017348</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6611,7 +6616,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6621,7 +6626,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6648,10 +6653,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131031498</v>
+        <v>131029927</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,50 +6664,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468224</v>
+        <v>468509</v>
       </c>
       <c r="R57" t="n">
-        <v>7017146</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6734,7 +6732,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6744,12 +6742,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6776,10 +6769,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131030174</v>
+        <v>131031498</v>
       </c>
       <c r="B58" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6787,39 +6780,50 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468273</v>
+        <v>468224</v>
       </c>
       <c r="R58" t="n">
-        <v>7017348</v>
+        <v>7017146</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6851,7 +6855,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6861,7 +6865,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6888,10 +6897,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131029927</v>
+        <v>131030313</v>
       </c>
       <c r="B59" t="n">
-        <v>58043</v>
+        <v>80349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6899,46 +6908,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468509</v>
+        <v>468321</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017305</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B66" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R66" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B67" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R67" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B70" t="n">
-        <v>79244</v>
+        <v>92107</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R70" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B71" t="n">
         <v>79244</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R71" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8339,10 +8339,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051508</v>
+        <v>131051494</v>
       </c>
       <c r="B73" t="n">
-        <v>92107</v>
+        <v>79244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468291</v>
+        <v>468190</v>
       </c>
       <c r="R73" t="n">
-        <v>7017134</v>
+        <v>7017343</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131051487</v>
+        <v>131051481</v>
       </c>
       <c r="B76" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8641,21 +8641,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468320</v>
+        <v>468333</v>
       </c>
       <c r="R76" t="n">
-        <v>7017296</v>
+        <v>7017253</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131051481</v>
+        <v>131051487</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8738,21 +8738,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468333</v>
+        <v>468320</v>
       </c>
       <c r="R77" t="n">
-        <v>7017253</v>
+        <v>7017296</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9222,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051489</v>
+        <v>131051496</v>
       </c>
       <c r="B82" t="n">
-        <v>79244</v>
+        <v>91809</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468318</v>
+        <v>468306</v>
       </c>
       <c r="R82" t="n">
-        <v>7017322</v>
+        <v>7017299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9293,11 +9293,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9324,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051496</v>
+        <v>131051489</v>
       </c>
       <c r="B83" t="n">
-        <v>91809</v>
+        <v>79244</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9335,21 +9330,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9359,10 +9354,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468306</v>
+        <v>468318</v>
       </c>
       <c r="R83" t="n">
-        <v>7017299</v>
+        <v>7017322</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9395,6 +9390,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,7 +9514,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B85" t="n">
         <v>91809</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R85" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051486</v>
+        <v>131051498</v>
       </c>
       <c r="B86" t="n">
         <v>91809</v>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R86" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131051503</v>
+        <v>131051495</v>
       </c>
       <c r="B87" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468303</v>
+        <v>468306</v>
       </c>
       <c r="R87" t="n">
-        <v>7017139</v>
+        <v>7017299</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131051495</v>
+        <v>131051503</v>
       </c>
       <c r="B88" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468306</v>
+        <v>468303</v>
       </c>
       <c r="R88" t="n">
-        <v>7017299</v>
+        <v>7017139</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051512</v>
+        <v>131051513</v>
       </c>
       <c r="B89" t="n">
-        <v>91809</v>
+        <v>92107</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468093</v>
+        <v>468342</v>
       </c>
       <c r="R89" t="n">
-        <v>7017305</v>
+        <v>7017232</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051513</v>
+        <v>131051512</v>
       </c>
       <c r="B90" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468342</v>
+        <v>468093</v>
       </c>
       <c r="R90" t="n">
-        <v>7017232</v>
+        <v>7017305</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -2765,10 +2765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865266</v>
+        <v>130865254</v>
       </c>
       <c r="B23" t="n">
-        <v>91805</v>
+        <v>57881</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,34 +2776,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468470</v>
+        <v>468479</v>
       </c>
       <c r="R23" t="n">
-        <v>7017481</v>
+        <v>7017488</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2835,7 +2840,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2845,7 +2850,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bearbetad grov död gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2872,10 +2882,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130865254</v>
+        <v>130865266</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>91805</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2883,39 +2893,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468479</v>
+        <v>468470</v>
       </c>
       <c r="R24" t="n">
-        <v>7017488</v>
+        <v>7017481</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,7 +2952,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2957,12 +2962,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetad grov död gran</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865182</v>
+        <v>130865004</v>
       </c>
       <c r="B25" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3000,34 +3000,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468493</v>
+        <v>468518</v>
       </c>
       <c r="R25" t="n">
-        <v>7017468</v>
+        <v>7017522</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3059,7 +3064,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3069,7 +3074,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3096,10 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865004</v>
+        <v>130865182</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3107,39 +3117,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468518</v>
+        <v>468493</v>
       </c>
       <c r="R26" t="n">
-        <v>7017522</v>
+        <v>7017468</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,7 +3176,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3181,12 +3186,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131031771</v>
+        <v>131030403</v>
       </c>
       <c r="B45" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,34 +5315,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468053</v>
+        <v>468347</v>
       </c>
       <c r="R45" t="n">
-        <v>7017383</v>
+        <v>7017234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5384,7 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5411,7 +5421,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030403</v>
+        <v>131030207</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5451,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468347</v>
+        <v>468282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017234</v>
+        <v>7017338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5496,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5538,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030207</v>
+        <v>131030656</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5559,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5568,13 +5578,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468282</v>
+        <v>468332</v>
       </c>
       <c r="R47" t="n">
-        <v>7017338</v>
+        <v>7017164</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5603,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5613,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131030656</v>
+        <v>131031771</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5656,39 +5666,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468332</v>
+        <v>468053</v>
       </c>
       <c r="R48" t="n">
-        <v>7017164</v>
+        <v>7017383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,7 +5725,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5730,12 +5735,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131031626</v>
+        <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5773,39 +5773,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468198</v>
+        <v>468269</v>
       </c>
       <c r="R49" t="n">
-        <v>7017261</v>
+        <v>7017349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5837,7 +5832,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5847,12 +5842,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5879,10 +5869,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131030164</v>
+        <v>131031626</v>
       </c>
       <c r="B50" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5890,34 +5880,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468269</v>
+        <v>468198</v>
       </c>
       <c r="R50" t="n">
-        <v>7017349</v>
+        <v>7017261</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5944,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5959,7 +5954,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030174</v>
+        <v>131030313</v>
       </c>
       <c r="B56" t="n">
-        <v>58043</v>
+        <v>80349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,42 +6552,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468273</v>
+        <v>468321</v>
       </c>
       <c r="R56" t="n">
-        <v>7017348</v>
+        <v>7017305</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6616,7 +6611,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6626,7 +6621,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6653,7 +6648,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131029927</v>
+        <v>131030174</v>
       </c>
       <c r="B57" t="n">
         <v>58043</v>
@@ -6681,11 +6676,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6693,14 +6684,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468509</v>
+        <v>468273</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017348</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6732,7 +6723,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6742,7 +6733,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,10 +6760,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131031498</v>
+        <v>131029927</v>
       </c>
       <c r="B58" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,50 +6771,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468224</v>
+        <v>468509</v>
       </c>
       <c r="R58" t="n">
-        <v>7017146</v>
+        <v>7017474</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6855,7 +6839,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6865,12 +6849,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6897,10 +6876,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131030313</v>
+        <v>131031498</v>
       </c>
       <c r="B59" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6908,37 +6887,53 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468321</v>
+        <v>468224</v>
       </c>
       <c r="R59" t="n">
-        <v>7017305</v>
+        <v>7017146</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6962,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6972,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7111,54 +7111,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031510</v>
+        <v>131031735</v>
       </c>
       <c r="B61" t="n">
-        <v>58256</v>
+        <v>91805</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468222</v>
+        <v>468074</v>
       </c>
       <c r="R61" t="n">
-        <v>7017146</v>
+        <v>7017313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7190,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7200,7 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7227,10 +7218,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031735</v>
+        <v>131031575</v>
       </c>
       <c r="B62" t="n">
-        <v>91805</v>
+        <v>80349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7238,21 +7229,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7262,10 +7253,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468074</v>
+        <v>468209</v>
       </c>
       <c r="R62" t="n">
-        <v>7017313</v>
+        <v>7017210</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7297,7 +7288,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7307,7 +7298,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7334,45 +7330,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031575</v>
+        <v>131031510</v>
       </c>
       <c r="B63" t="n">
-        <v>80349</v>
+        <v>58256</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468209</v>
+        <v>468222</v>
       </c>
       <c r="R63" t="n">
-        <v>7017210</v>
+        <v>7017146</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7404,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7414,12 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051508</v>
+        <v>131051494</v>
       </c>
       <c r="B70" t="n">
-        <v>92107</v>
+        <v>79244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468291</v>
+        <v>468190</v>
       </c>
       <c r="R70" t="n">
-        <v>7017134</v>
+        <v>7017343</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051511</v>
+        <v>131051490</v>
       </c>
       <c r="B71" t="n">
         <v>79244</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468075</v>
+        <v>468271</v>
       </c>
       <c r="R71" t="n">
-        <v>7017357</v>
+        <v>7017382</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8211,6 +8211,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8237,10 +8242,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051490</v>
+        <v>131051508</v>
       </c>
       <c r="B72" t="n">
-        <v>79244</v>
+        <v>92107</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8248,21 +8253,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8272,10 +8277,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468271</v>
+        <v>468291</v>
       </c>
       <c r="R72" t="n">
-        <v>7017382</v>
+        <v>7017134</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,11 +8313,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,7 +8339,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B73" t="n">
         <v>79244</v>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R73" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8630,10 +8630,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131051481</v>
+        <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8641,21 +8641,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8665,10 +8665,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468333</v>
+        <v>468320</v>
       </c>
       <c r="R76" t="n">
-        <v>7017253</v>
+        <v>7017296</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8727,10 +8727,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131051487</v>
+        <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8738,21 +8738,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8762,10 +8762,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468320</v>
+        <v>468333</v>
       </c>
       <c r="R77" t="n">
-        <v>7017296</v>
+        <v>7017253</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9028,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051492</v>
+        <v>131051482</v>
       </c>
       <c r="B80" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,21 +9039,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468247</v>
+        <v>468092</v>
       </c>
       <c r="R80" t="n">
-        <v>7017186</v>
+        <v>7017317</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9125,10 +9125,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051482</v>
+        <v>131051492</v>
       </c>
       <c r="B81" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,21 +9136,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468092</v>
+        <v>468247</v>
       </c>
       <c r="R81" t="n">
-        <v>7017317</v>
+        <v>7017186</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9514,7 +9514,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051486</v>
+        <v>131051498</v>
       </c>
       <c r="B85" t="n">
         <v>91809</v>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R85" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,7 +9611,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B86" t="n">
         <v>91809</v>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R86" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9708,10 +9708,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131051495</v>
+        <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>80349</v>
+        <v>79244</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9719,21 +9719,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9743,10 +9743,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468306</v>
+        <v>468303</v>
       </c>
       <c r="R87" t="n">
-        <v>7017299</v>
+        <v>7017139</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9805,10 +9805,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131051503</v>
+        <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>79244</v>
+        <v>80349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9816,21 +9816,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9840,10 +9840,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468303</v>
+        <v>468306</v>
       </c>
       <c r="R88" t="n">
-        <v>7017139</v>
+        <v>7017299</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051513</v>
+        <v>131051512</v>
       </c>
       <c r="B89" t="n">
-        <v>92107</v>
+        <v>91809</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468342</v>
+        <v>468093</v>
       </c>
       <c r="R89" t="n">
-        <v>7017232</v>
+        <v>7017305</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051512</v>
+        <v>131051513</v>
       </c>
       <c r="B90" t="n">
-        <v>91809</v>
+        <v>92107</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468093</v>
+        <v>468342</v>
       </c>
       <c r="R90" t="n">
-        <v>7017305</v>
+        <v>7017232</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -2765,10 +2765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865254</v>
+        <v>130865266</v>
       </c>
       <c r="B23" t="n">
-        <v>57881</v>
+        <v>91805</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2776,39 +2776,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468479</v>
+        <v>468470</v>
       </c>
       <c r="R23" t="n">
-        <v>7017488</v>
+        <v>7017481</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2840,7 +2835,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2850,12 +2845,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Bearbetad grov död gran</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2882,10 +2872,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130865266</v>
+        <v>130865254</v>
       </c>
       <c r="B24" t="n">
-        <v>91805</v>
+        <v>57881</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2893,34 +2883,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1108</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468470</v>
+        <v>468479</v>
       </c>
       <c r="R24" t="n">
-        <v>7017481</v>
+        <v>7017488</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,7 +2947,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2962,7 +2957,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bearbetad grov död gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2989,10 +2989,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865004</v>
+        <v>130865182</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3000,39 +3000,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468518</v>
+        <v>468493</v>
       </c>
       <c r="R25" t="n">
-        <v>7017522</v>
+        <v>7017468</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3064,7 +3059,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3074,12 +3069,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3106,10 +3096,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865182</v>
+        <v>130865004</v>
       </c>
       <c r="B26" t="n">
-        <v>91809</v>
+        <v>57884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,34 +3107,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468493</v>
+        <v>468518</v>
       </c>
       <c r="R26" t="n">
-        <v>7017468</v>
+        <v>7017522</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3171,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3186,7 +3181,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3793,10 +3793,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130865481</v>
+        <v>130865014</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>58043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3804,34 +3804,43 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468481</v>
+        <v>468521</v>
       </c>
       <c r="R32" t="n">
-        <v>7017551</v>
+        <v>7017519</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3863,7 +3872,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3873,7 +3882,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3900,10 +3909,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130865014</v>
+        <v>130865481</v>
       </c>
       <c r="B33" t="n">
-        <v>58043</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3911,43 +3920,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468521</v>
+        <v>468481</v>
       </c>
       <c r="R33" t="n">
-        <v>7017519</v>
+        <v>7017551</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131031743</v>
+        <v>131029902</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,34 +5082,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468070</v>
+        <v>468507</v>
       </c>
       <c r="R43" t="n">
-        <v>7017311</v>
+        <v>7017469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,7 +5155,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5151,7 +5165,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5178,10 +5197,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131029902</v>
+        <v>131031743</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,48 +5208,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468507</v>
+        <v>468070</v>
       </c>
       <c r="R44" t="n">
-        <v>7017469</v>
+        <v>7017311</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,7 +5267,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,12 +5277,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,7 +5304,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030403</v>
+        <v>131030207</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5344,13 +5344,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468347</v>
+        <v>468282</v>
       </c>
       <c r="R45" t="n">
-        <v>7017234</v>
+        <v>7017338</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030207</v>
+        <v>131030656</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5452,7 +5452,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468282</v>
+        <v>468332</v>
       </c>
       <c r="R46" t="n">
-        <v>7017338</v>
+        <v>7017164</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,7 +5538,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030656</v>
+        <v>131030403</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5569,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468332</v>
+        <v>468347</v>
       </c>
       <c r="R47" t="n">
-        <v>7017164</v>
+        <v>7017234</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6648,10 +6648,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131030174</v>
+        <v>131031498</v>
       </c>
       <c r="B57" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,39 +6659,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468273</v>
+        <v>468224</v>
       </c>
       <c r="R57" t="n">
-        <v>7017348</v>
+        <v>7017146</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6723,7 +6734,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6733,7 +6744,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6760,7 +6776,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131029927</v>
+        <v>131030174</v>
       </c>
       <c r="B58" t="n">
         <v>58043</v>
@@ -6788,11 +6804,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6800,14 +6812,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468509</v>
+        <v>468273</v>
       </c>
       <c r="R58" t="n">
-        <v>7017474</v>
+        <v>7017348</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6839,7 +6851,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6849,7 +6861,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6876,10 +6888,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131031498</v>
+        <v>131029927</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6887,50 +6899,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468224</v>
+        <v>468509</v>
       </c>
       <c r="R59" t="n">
-        <v>7017146</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6962,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6972,12 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B66" t="n">
-        <v>91805</v>
+        <v>79244</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R66" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B67" t="n">
-        <v>79244</v>
+        <v>91805</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R67" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B70" t="n">
         <v>79244</v>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R70" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051490</v>
+        <v>131051494</v>
       </c>
       <c r="B71" t="n">
         <v>79244</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468271</v>
+        <v>468190</v>
       </c>
       <c r="R71" t="n">
-        <v>7017382</v>
+        <v>7017343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8211,11 +8211,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8242,10 +8237,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051508</v>
+        <v>131051490</v>
       </c>
       <c r="B72" t="n">
-        <v>92107</v>
+        <v>79244</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8253,21 +8248,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8277,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468291</v>
+        <v>468271</v>
       </c>
       <c r="R72" t="n">
-        <v>7017134</v>
+        <v>7017382</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8313,6 +8308,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,10 +8339,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>79244</v>
+        <v>92107</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8350,21 +8350,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R73" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051497</v>
+        <v>131051498</v>
       </c>
       <c r="B84" t="n">
-        <v>91829</v>
+        <v>91809</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,19 +9432,23 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9514,7 +9518,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B85" t="n">
         <v>91809</v>
@@ -9549,10 +9553,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R85" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,10 +9615,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051486</v>
+        <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91809</v>
+        <v>91829</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9622,23 +9626,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R86" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -4135,7 +4135,7 @@
         <v>131014503</v>
       </c>
       <c r="B35" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>131005337</v>
       </c>
       <c r="B39" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131029902</v>
+        <v>131031743</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,48 +5082,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468507</v>
+        <v>468070</v>
       </c>
       <c r="R43" t="n">
-        <v>7017469</v>
+        <v>7017311</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5155,7 +5141,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,12 +5151,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5197,10 +5178,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131031743</v>
+        <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5208,34 +5189,48 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468070</v>
+        <v>468507</v>
       </c>
       <c r="R44" t="n">
-        <v>7017311</v>
+        <v>7017469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5267,7 +5262,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5277,7 +5272,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,7 +5304,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030207</v>
+        <v>131030403</v>
       </c>
       <c r="B45" t="n">
         <v>57884</v>
@@ -5344,13 +5344,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468282</v>
+        <v>468347</v>
       </c>
       <c r="R45" t="n">
-        <v>7017338</v>
+        <v>7017234</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5389,12 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,7 +5421,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030656</v>
+        <v>131030207</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5452,7 +5452,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468332</v>
+        <v>468282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017164</v>
+        <v>7017338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,7 +5538,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030403</v>
+        <v>131030656</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5569,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468347</v>
+        <v>468332</v>
       </c>
       <c r="R47" t="n">
-        <v>7017234</v>
+        <v>7017164</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5658,7 +5658,7 @@
         <v>131031771</v>
       </c>
       <c r="B48" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>131030316</v>
       </c>
       <c r="B51" t="n">
-        <v>80378</v>
+        <v>80379</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>131030066</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>131031769</v>
       </c>
       <c r="B55" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030313</v>
+        <v>131031498</v>
       </c>
       <c r="B56" t="n">
-        <v>80349</v>
+        <v>57884</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,37 +6552,53 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468321</v>
+        <v>468224</v>
       </c>
       <c r="R56" t="n">
-        <v>7017305</v>
+        <v>7017146</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6611,7 +6627,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6621,7 +6637,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6648,10 +6669,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131031498</v>
+        <v>131030174</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,50 +6680,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468224</v>
+        <v>468273</v>
       </c>
       <c r="R57" t="n">
-        <v>7017146</v>
+        <v>7017348</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6734,7 +6744,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6744,12 +6754,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6776,7 +6781,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131030174</v>
+        <v>131029927</v>
       </c>
       <c r="B58" t="n">
         <v>58043</v>
@@ -6804,7 +6809,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6812,14 +6821,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468273</v>
+        <v>468509</v>
       </c>
       <c r="R58" t="n">
-        <v>7017348</v>
+        <v>7017474</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6851,7 +6860,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6861,7 +6870,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6888,10 +6897,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131029927</v>
+        <v>131030313</v>
       </c>
       <c r="B59" t="n">
-        <v>58043</v>
+        <v>80350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6899,46 +6908,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468509</v>
+        <v>468321</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017305</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7007,7 +7007,7 @@
         <v>131030168</v>
       </c>
       <c r="B60" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031735</v>
+        <v>131031575</v>
       </c>
       <c r="B61" t="n">
-        <v>91805</v>
+        <v>80350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468074</v>
+        <v>468209</v>
       </c>
       <c r="R61" t="n">
-        <v>7017313</v>
+        <v>7017210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7191,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7218,45 +7223,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031575</v>
+        <v>131031510</v>
       </c>
       <c r="B62" t="n">
-        <v>80349</v>
+        <v>58256</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468209</v>
+        <v>468222</v>
       </c>
       <c r="R62" t="n">
-        <v>7017210</v>
+        <v>7017146</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7288,7 +7302,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7298,12 +7312,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7330,54 +7339,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031510</v>
+        <v>131031735</v>
       </c>
       <c r="B63" t="n">
-        <v>58256</v>
+        <v>91806</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468222</v>
+        <v>468074</v>
       </c>
       <c r="R63" t="n">
-        <v>7017146</v>
+        <v>7017313</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7551,7 +7551,7 @@
         <v>131030429</v>
       </c>
       <c r="B65" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B66" t="n">
-        <v>79244</v>
+        <v>91806</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R66" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B67" t="n">
-        <v>91805</v>
+        <v>79245</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R67" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>131051506</v>
       </c>
       <c r="B68" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>131051511</v>
       </c>
       <c r="B70" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>131051494</v>
       </c>
       <c r="B71" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>131051490</v>
       </c>
       <c r="B72" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>131051483</v>
       </c>
       <c r="B78" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051482</v>
+        <v>131051492</v>
       </c>
       <c r="B80" t="n">
-        <v>91805</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,21 +9039,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468092</v>
+        <v>468247</v>
       </c>
       <c r="R80" t="n">
-        <v>7017317</v>
+        <v>7017186</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9125,10 +9125,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051492</v>
+        <v>131051482</v>
       </c>
       <c r="B81" t="n">
-        <v>79244</v>
+        <v>91806</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,21 +9136,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468247</v>
+        <v>468092</v>
       </c>
       <c r="R81" t="n">
-        <v>7017186</v>
+        <v>7017317</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9225,7 +9225,7 @@
         <v>131051496</v>
       </c>
       <c r="B82" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>131051489</v>
       </c>
       <c r="B83" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>131051498</v>
       </c>
       <c r="B84" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>131051486</v>
       </c>
       <c r="B85" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>80349</v>
+        <v>80350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131051512</v>
       </c>
       <c r="B89" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>131051513</v>
       </c>
       <c r="B90" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030403</v>
+        <v>131031771</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,39 +5315,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468347</v>
+        <v>468053</v>
       </c>
       <c r="R45" t="n">
-        <v>7017234</v>
+        <v>7017383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5374,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5389,12 +5384,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,7 +5411,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030207</v>
+        <v>131030403</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5461,13 +5451,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468282</v>
+        <v>468347</v>
       </c>
       <c r="R46" t="n">
-        <v>7017338</v>
+        <v>7017234</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5496,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,7 +5528,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030656</v>
+        <v>131030207</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5569,7 +5559,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5578,13 +5568,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468332</v>
+        <v>468282</v>
       </c>
       <c r="R47" t="n">
-        <v>7017164</v>
+        <v>7017338</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5613,7 +5603,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5623,12 +5613,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5655,10 +5645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131031771</v>
+        <v>131030656</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,34 +5656,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468053</v>
+        <v>468332</v>
       </c>
       <c r="R48" t="n">
-        <v>7017383</v>
+        <v>7017164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,7 +5720,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5735,7 +5730,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B70" t="n">
-        <v>79245</v>
+        <v>92108</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R70" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B71" t="n">
         <v>79245</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R71" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051490</v>
+        <v>131051494</v>
       </c>
       <c r="B72" t="n">
         <v>79245</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468271</v>
+        <v>468190</v>
       </c>
       <c r="R72" t="n">
-        <v>7017382</v>
+        <v>7017343</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,11 +8308,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,10 +8334,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051508</v>
+        <v>131051490</v>
       </c>
       <c r="B73" t="n">
-        <v>92108</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8350,21 +8345,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8374,10 +8369,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468291</v>
+        <v>468271</v>
       </c>
       <c r="R73" t="n">
-        <v>7017134</v>
+        <v>7017382</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8410,6 +8405,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD73" t="b">

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031575</v>
+        <v>131031735</v>
       </c>
       <c r="B61" t="n">
-        <v>80350</v>
+        <v>91806</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468209</v>
+        <v>468074</v>
       </c>
       <c r="R61" t="n">
-        <v>7017210</v>
+        <v>7017313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,12 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7223,54 +7218,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031510</v>
+        <v>131031575</v>
       </c>
       <c r="B62" t="n">
-        <v>58256</v>
+        <v>80350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468222</v>
+        <v>468209</v>
       </c>
       <c r="R62" t="n">
-        <v>7017146</v>
+        <v>7017210</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7302,7 +7288,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7312,7 +7298,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7339,45 +7330,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031735</v>
+        <v>131031510</v>
       </c>
       <c r="B63" t="n">
-        <v>91806</v>
+        <v>58256</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468074</v>
+        <v>468222</v>
       </c>
       <c r="R63" t="n">
-        <v>7017313</v>
+        <v>7017146</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B66" t="n">
-        <v>91806</v>
+        <v>79245</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R66" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B67" t="n">
-        <v>79245</v>
+        <v>91806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R67" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051508</v>
+        <v>131051511</v>
       </c>
       <c r="B70" t="n">
-        <v>92108</v>
+        <v>79245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468291</v>
+        <v>468075</v>
       </c>
       <c r="R70" t="n">
-        <v>7017134</v>
+        <v>7017357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051511</v>
+        <v>131051494</v>
       </c>
       <c r="B71" t="n">
         <v>79245</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468075</v>
+        <v>468190</v>
       </c>
       <c r="R71" t="n">
-        <v>7017357</v>
+        <v>7017343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051494</v>
+        <v>131051490</v>
       </c>
       <c r="B72" t="n">
         <v>79245</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468190</v>
+        <v>468271</v>
       </c>
       <c r="R72" t="n">
-        <v>7017343</v>
+        <v>7017382</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,6 +8308,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8334,10 +8339,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051490</v>
+        <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>92108</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8345,21 +8350,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8369,10 +8374,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468271</v>
+        <v>468291</v>
       </c>
       <c r="R73" t="n">
-        <v>7017382</v>
+        <v>7017134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8405,11 +8410,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8824,10 +8824,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131051483</v>
+        <v>131051491</v>
       </c>
       <c r="B78" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,34 +8835,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468300</v>
+        <v>468383</v>
       </c>
       <c r="R78" t="n">
-        <v>7017272</v>
+        <v>7017207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8895,6 +8900,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8921,10 +8931,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131051491</v>
+        <v>131051483</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8932,39 +8942,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468383</v>
+        <v>468300</v>
       </c>
       <c r="R79" t="n">
-        <v>7017207</v>
+        <v>7017272</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8997,11 +9002,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9028,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051492</v>
+        <v>131051482</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>91806</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,21 +9039,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468247</v>
+        <v>468092</v>
       </c>
       <c r="R80" t="n">
-        <v>7017186</v>
+        <v>7017317</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9125,10 +9125,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051482</v>
+        <v>131051492</v>
       </c>
       <c r="B81" t="n">
-        <v>91806</v>
+        <v>79245</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,21 +9136,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468092</v>
+        <v>468247</v>
       </c>
       <c r="R81" t="n">
-        <v>7017317</v>
+        <v>7017186</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B84" t="n">
         <v>91810</v>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R84" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9518,10 +9518,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051486</v>
+        <v>131051497</v>
       </c>
       <c r="B85" t="n">
-        <v>91810</v>
+        <v>91830</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9529,23 +9529,19 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9553,10 +9549,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R85" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9615,10 +9611,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051497</v>
+        <v>131051498</v>
       </c>
       <c r="B86" t="n">
-        <v>91830</v>
+        <v>91810</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9626,19 +9622,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -4135,7 +4135,7 @@
         <v>131014503</v>
       </c>
       <c r="B35" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131031743</v>
+        <v>131029902</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,34 +5082,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468070</v>
+        <v>468507</v>
       </c>
       <c r="R43" t="n">
-        <v>7017311</v>
+        <v>7017469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5141,7 +5155,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5151,7 +5165,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5178,10 +5197,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131029902</v>
+        <v>131031743</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,48 +5208,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468507</v>
+        <v>468070</v>
       </c>
       <c r="R44" t="n">
-        <v>7017469</v>
+        <v>7017311</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5262,7 +5267,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5272,12 +5277,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131031771</v>
+        <v>131030403</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,34 +5315,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468053</v>
+        <v>468347</v>
       </c>
       <c r="R45" t="n">
-        <v>7017383</v>
+        <v>7017234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5384,7 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5411,7 +5421,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030403</v>
+        <v>131030207</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5451,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468347</v>
+        <v>468282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017234</v>
+        <v>7017338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5496,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5538,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030207</v>
+        <v>131030656</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5559,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5568,13 +5578,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468282</v>
+        <v>468332</v>
       </c>
       <c r="R47" t="n">
-        <v>7017338</v>
+        <v>7017164</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5603,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5613,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131030656</v>
+        <v>131031771</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5656,39 +5666,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468332</v>
+        <v>468053</v>
       </c>
       <c r="R48" t="n">
-        <v>7017164</v>
+        <v>7017383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,7 +5725,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5730,12 +5735,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5765,7 +5765,7 @@
         <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>131031769</v>
       </c>
       <c r="B55" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131031498</v>
+        <v>131030174</v>
       </c>
       <c r="B56" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,50 +6552,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468224</v>
+        <v>468273</v>
       </c>
       <c r="R56" t="n">
-        <v>7017146</v>
+        <v>7017348</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6627,7 +6616,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6637,12 +6626,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6669,7 +6653,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131030174</v>
+        <v>131029927</v>
       </c>
       <c r="B57" t="n">
         <v>58043</v>
@@ -6697,7 +6681,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6705,14 +6693,14 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468273</v>
+        <v>468509</v>
       </c>
       <c r="R57" t="n">
-        <v>7017348</v>
+        <v>7017474</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6744,7 +6732,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6754,7 +6742,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6781,10 +6769,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131029927</v>
+        <v>131030313</v>
       </c>
       <c r="B58" t="n">
-        <v>58043</v>
+        <v>80350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6792,46 +6780,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468509</v>
+        <v>468321</v>
       </c>
       <c r="R58" t="n">
-        <v>7017474</v>
+        <v>7017305</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6860,7 +6839,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6870,7 +6849,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6897,10 +6876,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131030313</v>
+        <v>131031498</v>
       </c>
       <c r="B59" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6908,37 +6887,53 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468321</v>
+        <v>468224</v>
       </c>
       <c r="R59" t="n">
-        <v>7017305</v>
+        <v>7017146</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6962,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6972,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031735</v>
+        <v>131031575</v>
       </c>
       <c r="B61" t="n">
-        <v>91806</v>
+        <v>80350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468074</v>
+        <v>468209</v>
       </c>
       <c r="R61" t="n">
-        <v>7017313</v>
+        <v>7017210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7191,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7218,45 +7223,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031575</v>
+        <v>131031510</v>
       </c>
       <c r="B62" t="n">
-        <v>80350</v>
+        <v>58256</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468209</v>
+        <v>468222</v>
       </c>
       <c r="R62" t="n">
-        <v>7017210</v>
+        <v>7017146</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7288,7 +7302,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7298,12 +7312,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7330,54 +7339,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031510</v>
+        <v>131031735</v>
       </c>
       <c r="B63" t="n">
-        <v>58256</v>
+        <v>91809</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468222</v>
+        <v>468074</v>
       </c>
       <c r="R63" t="n">
-        <v>7017146</v>
+        <v>7017313</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7755,7 +7755,7 @@
         <v>131051493</v>
       </c>
       <c r="B67" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8824,10 +8824,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131051491</v>
+        <v>131051483</v>
       </c>
       <c r="B78" t="n">
-        <v>57884</v>
+        <v>80350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,39 +8835,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468383</v>
+        <v>468300</v>
       </c>
       <c r="R78" t="n">
-        <v>7017207</v>
+        <v>7017272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8900,11 +8895,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8931,10 +8921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131051483</v>
+        <v>131051491</v>
       </c>
       <c r="B79" t="n">
-        <v>80350</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8942,34 +8932,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468300</v>
+        <v>468383</v>
       </c>
       <c r="R79" t="n">
-        <v>7017272</v>
+        <v>7017207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9002,6 +8997,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9031,7 +9031,7 @@
         <v>131051482</v>
       </c>
       <c r="B80" t="n">
-        <v>91806</v>
+        <v>91809</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>131051496</v>
       </c>
       <c r="B82" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051486</v>
+        <v>131051498</v>
       </c>
       <c r="B84" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9456,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R84" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9518,10 +9518,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051497</v>
+        <v>131051486</v>
       </c>
       <c r="B85" t="n">
-        <v>91830</v>
+        <v>91813</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9529,19 +9529,23 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9549,10 +9553,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R85" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,10 +9615,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051498</v>
+        <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91810</v>
+        <v>91833</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9622,23 +9626,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131051512</v>
       </c>
       <c r="B89" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>131051513</v>
       </c>
       <c r="B90" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -4135,7 +4135,7 @@
         <v>131014503</v>
       </c>
       <c r="B35" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>131005337</v>
       </c>
       <c r="B39" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5071,10 +5071,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131029902</v>
+        <v>131031743</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,48 +5082,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468507</v>
+        <v>468070</v>
       </c>
       <c r="R43" t="n">
-        <v>7017469</v>
+        <v>7017311</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5155,7 +5141,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5165,12 +5151,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5197,10 +5178,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131031743</v>
+        <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5208,34 +5189,48 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468070</v>
+        <v>468507</v>
       </c>
       <c r="R44" t="n">
-        <v>7017311</v>
+        <v>7017469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5267,7 +5262,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5277,7 +5272,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030403</v>
+        <v>131031771</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,39 +5315,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468347</v>
+        <v>468053</v>
       </c>
       <c r="R45" t="n">
-        <v>7017234</v>
+        <v>7017383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5374,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5389,12 +5384,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,7 +5411,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030207</v>
+        <v>131030403</v>
       </c>
       <c r="B46" t="n">
         <v>57884</v>
@@ -5461,13 +5451,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468282</v>
+        <v>468347</v>
       </c>
       <c r="R46" t="n">
-        <v>7017338</v>
+        <v>7017234</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5496,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,7 +5528,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030656</v>
+        <v>131030207</v>
       </c>
       <c r="B47" t="n">
         <v>57884</v>
@@ -5569,7 +5559,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5578,13 +5568,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468332</v>
+        <v>468282</v>
       </c>
       <c r="R47" t="n">
-        <v>7017164</v>
+        <v>7017338</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5613,7 +5603,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5623,12 +5613,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5655,10 +5645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131031771</v>
+        <v>131030656</v>
       </c>
       <c r="B48" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,34 +5656,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468053</v>
+        <v>468332</v>
       </c>
       <c r="R48" t="n">
-        <v>7017383</v>
+        <v>7017164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,7 +5720,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5735,7 +5730,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5765,7 +5765,7 @@
         <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>131030316</v>
       </c>
       <c r="B51" t="n">
-        <v>80379</v>
+        <v>80380</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>131030066</v>
       </c>
       <c r="B52" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>131031769</v>
       </c>
       <c r="B55" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030174</v>
+        <v>131030313</v>
       </c>
       <c r="B56" t="n">
-        <v>58043</v>
+        <v>80351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,42 +6552,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468273</v>
+        <v>468321</v>
       </c>
       <c r="R56" t="n">
-        <v>7017348</v>
+        <v>7017305</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6616,7 +6611,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6626,7 +6621,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6653,10 +6648,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131029927</v>
+        <v>131031498</v>
       </c>
       <c r="B57" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6664,43 +6659,50 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468509</v>
+        <v>468224</v>
       </c>
       <c r="R57" t="n">
-        <v>7017474</v>
+        <v>7017146</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6732,7 +6734,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6742,7 +6744,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6769,10 +6776,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131030313</v>
+        <v>131030174</v>
       </c>
       <c r="B58" t="n">
-        <v>80350</v>
+        <v>58043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,37 +6787,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468321</v>
+        <v>468273</v>
       </c>
       <c r="R58" t="n">
-        <v>7017305</v>
+        <v>7017348</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6839,7 +6851,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6849,7 +6861,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6876,10 +6888,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131031498</v>
+        <v>131029927</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6887,50 +6899,43 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468224</v>
+        <v>468509</v>
       </c>
       <c r="R59" t="n">
-        <v>7017146</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6962,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6972,12 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7007,7 +7007,7 @@
         <v>131030168</v>
       </c>
       <c r="B60" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031575</v>
+        <v>131031735</v>
       </c>
       <c r="B61" t="n">
-        <v>80350</v>
+        <v>91810</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468209</v>
+        <v>468074</v>
       </c>
       <c r="R61" t="n">
-        <v>7017210</v>
+        <v>7017313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,12 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7223,54 +7218,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031510</v>
+        <v>131031575</v>
       </c>
       <c r="B62" t="n">
-        <v>58256</v>
+        <v>80351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468222</v>
+        <v>468209</v>
       </c>
       <c r="R62" t="n">
-        <v>7017146</v>
+        <v>7017210</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7302,7 +7288,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7312,7 +7298,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7339,45 +7330,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031735</v>
+        <v>131031510</v>
       </c>
       <c r="B63" t="n">
-        <v>91809</v>
+        <v>58256</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468074</v>
+        <v>468222</v>
       </c>
       <c r="R63" t="n">
-        <v>7017313</v>
+        <v>7017146</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7551,7 +7551,7 @@
         <v>131030429</v>
       </c>
       <c r="B65" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>131051504</v>
       </c>
       <c r="B66" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>131051493</v>
       </c>
       <c r="B67" t="n">
-        <v>91809</v>
+        <v>91810</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>131051506</v>
       </c>
       <c r="B68" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8046,7 +8046,7 @@
         <v>131051511</v>
       </c>
       <c r="B70" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>131051494</v>
       </c>
       <c r="B71" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8240,7 +8240,7 @@
         <v>131051490</v>
       </c>
       <c r="B72" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>131051483</v>
       </c>
       <c r="B78" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051482</v>
+        <v>131051492</v>
       </c>
       <c r="B80" t="n">
-        <v>91809</v>
+        <v>79246</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,21 +9039,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468092</v>
+        <v>468247</v>
       </c>
       <c r="R80" t="n">
-        <v>7017317</v>
+        <v>7017186</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9125,10 +9125,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051492</v>
+        <v>131051482</v>
       </c>
       <c r="B81" t="n">
-        <v>79245</v>
+        <v>91810</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,21 +9136,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468247</v>
+        <v>468092</v>
       </c>
       <c r="R81" t="n">
-        <v>7017186</v>
+        <v>7017317</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9222,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051496</v>
+        <v>131051489</v>
       </c>
       <c r="B82" t="n">
-        <v>91813</v>
+        <v>79246</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468306</v>
+        <v>468318</v>
       </c>
       <c r="R82" t="n">
-        <v>7017299</v>
+        <v>7017322</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9293,6 +9293,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9324,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051489</v>
+        <v>131051496</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>91814</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9330,21 +9335,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9354,10 +9359,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468318</v>
+        <v>468306</v>
       </c>
       <c r="R83" t="n">
-        <v>7017322</v>
+        <v>7017299</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9390,11 +9395,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9424,7 +9424,7 @@
         <v>131051498</v>
       </c>
       <c r="B84" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>131051486</v>
       </c>
       <c r="B85" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>131051512</v>
       </c>
       <c r="B89" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>131051513</v>
       </c>
       <c r="B90" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031735</v>
+        <v>131031575</v>
       </c>
       <c r="B61" t="n">
-        <v>91810</v>
+        <v>80351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468074</v>
+        <v>468209</v>
       </c>
       <c r="R61" t="n">
-        <v>7017313</v>
+        <v>7017210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7191,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7218,45 +7223,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031575</v>
+        <v>131031510</v>
       </c>
       <c r="B62" t="n">
-        <v>80351</v>
+        <v>58256</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>103015</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468209</v>
+        <v>468222</v>
       </c>
       <c r="R62" t="n">
-        <v>7017210</v>
+        <v>7017146</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7288,7 +7302,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7298,12 +7312,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7330,54 +7339,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031510</v>
+        <v>131031735</v>
       </c>
       <c r="B63" t="n">
-        <v>58256</v>
+        <v>91810</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468222</v>
+        <v>468074</v>
       </c>
       <c r="R63" t="n">
-        <v>7017146</v>
+        <v>7017313</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -4019,7 +4019,7 @@
         <v>131004176</v>
       </c>
       <c r="B34" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>131014503</v>
       </c>
       <c r="B35" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>131006989</v>
       </c>
       <c r="B36" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>131007096</v>
       </c>
       <c r="B37" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
         <v>131008392</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,7 +4607,7 @@
         <v>131005337</v>
       </c>
       <c r="B39" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>131004190</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>131007087</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
         <v>131031661</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>131031743</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131031771</v>
+        <v>131030403</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,34 +5315,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468053</v>
+        <v>468347</v>
       </c>
       <c r="R45" t="n">
-        <v>7017383</v>
+        <v>7017234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5384,7 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5411,10 +5421,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030403</v>
+        <v>131030207</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5451,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468347</v>
+        <v>468282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017234</v>
+        <v>7017338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5496,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,10 +5538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030207</v>
+        <v>131030656</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5559,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5568,13 +5578,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468282</v>
+        <v>468332</v>
       </c>
       <c r="R47" t="n">
-        <v>7017338</v>
+        <v>7017164</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5603,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5613,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131030656</v>
+        <v>131031771</v>
       </c>
       <c r="B48" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5656,39 +5666,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468332</v>
+        <v>468053</v>
       </c>
       <c r="R48" t="n">
-        <v>7017164</v>
+        <v>7017383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,7 +5725,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5730,12 +5735,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5765,7 +5765,7 @@
         <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5872,7 +5872,7 @@
         <v>131031626</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
         <v>131030316</v>
       </c>
       <c r="B51" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>131030066</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>131030182</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>131030305</v>
       </c>
       <c r="B54" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>131031769</v>
       </c>
       <c r="B55" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030313</v>
+        <v>131031498</v>
       </c>
       <c r="B56" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,37 +6552,53 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468321</v>
+        <v>468224</v>
       </c>
       <c r="R56" t="n">
-        <v>7017305</v>
+        <v>7017146</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6611,7 +6627,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6621,7 +6637,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6648,10 +6669,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131031498</v>
+        <v>131030174</v>
       </c>
       <c r="B57" t="n">
-        <v>57884</v>
+        <v>58045</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,50 +6680,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468224</v>
+        <v>468273</v>
       </c>
       <c r="R57" t="n">
-        <v>7017146</v>
+        <v>7017348</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6734,7 +6744,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6744,12 +6754,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6776,10 +6781,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131030174</v>
+        <v>131029927</v>
       </c>
       <c r="B58" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6804,7 +6809,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6812,14 +6821,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468273</v>
+        <v>468509</v>
       </c>
       <c r="R58" t="n">
-        <v>7017348</v>
+        <v>7017474</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6851,7 +6860,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6861,7 +6870,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6888,10 +6897,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131029927</v>
+        <v>131030313</v>
       </c>
       <c r="B59" t="n">
-        <v>58043</v>
+        <v>80353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6899,46 +6908,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468509</v>
+        <v>468321</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017305</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7007,7 +7007,7 @@
         <v>131030168</v>
       </c>
       <c r="B60" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031575</v>
+        <v>131031735</v>
       </c>
       <c r="B61" t="n">
-        <v>80351</v>
+        <v>91812</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468209</v>
+        <v>468074</v>
       </c>
       <c r="R61" t="n">
-        <v>7017210</v>
+        <v>7017313</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,12 +7191,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7223,54 +7218,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031510</v>
+        <v>131031575</v>
       </c>
       <c r="B62" t="n">
-        <v>58256</v>
+        <v>80353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468222</v>
+        <v>468209</v>
       </c>
       <c r="R62" t="n">
-        <v>7017146</v>
+        <v>7017210</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7302,7 +7288,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7312,7 +7298,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7339,45 +7330,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031735</v>
+        <v>131031510</v>
       </c>
       <c r="B63" t="n">
-        <v>91810</v>
+        <v>58258</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1108</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468074</v>
+        <v>468222</v>
       </c>
       <c r="R63" t="n">
-        <v>7017313</v>
+        <v>7017146</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7409,7 +7409,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7449,7 +7449,7 @@
         <v>131035155</v>
       </c>
       <c r="B64" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>131030429</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B66" t="n">
-        <v>79246</v>
+        <v>91812</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R66" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B67" t="n">
-        <v>91810</v>
+        <v>79248</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R67" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>131051506</v>
       </c>
       <c r="B68" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B70" t="n">
-        <v>79246</v>
+        <v>92114</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R70" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B71" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R71" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,10 +8237,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051490</v>
+        <v>131051494</v>
       </c>
       <c r="B72" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468271</v>
+        <v>468190</v>
       </c>
       <c r="R72" t="n">
-        <v>7017382</v>
+        <v>7017343</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,11 +8308,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,10 +8334,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051508</v>
+        <v>131051490</v>
       </c>
       <c r="B73" t="n">
-        <v>92112</v>
+        <v>79248</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8350,21 +8345,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8374,10 +8369,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468291</v>
+        <v>468271</v>
       </c>
       <c r="R73" t="n">
-        <v>7017134</v>
+        <v>7017382</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8410,6 +8405,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8824,10 +8824,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131051483</v>
+        <v>131051491</v>
       </c>
       <c r="B78" t="n">
-        <v>80351</v>
+        <v>57886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,34 +8835,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468300</v>
+        <v>468383</v>
       </c>
       <c r="R78" t="n">
-        <v>7017272</v>
+        <v>7017207</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8895,6 +8900,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8921,10 +8931,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131051491</v>
+        <v>131051483</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>80353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8932,39 +8942,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468383</v>
+        <v>468300</v>
       </c>
       <c r="R79" t="n">
-        <v>7017207</v>
+        <v>7017272</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8997,11 +9002,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9031,7 +9031,7 @@
         <v>131051492</v>
       </c>
       <c r="B80" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>131051482</v>
       </c>
       <c r="B81" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>131051489</v>
       </c>
       <c r="B82" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9327,7 +9327,7 @@
         <v>131051496</v>
       </c>
       <c r="B83" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051498</v>
+        <v>131051497</v>
       </c>
       <c r="B84" t="n">
-        <v>91814</v>
+        <v>91836</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,23 +9432,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9521,7 +9517,7 @@
         <v>131051486</v>
       </c>
       <c r="B85" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9615,10 +9611,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051497</v>
+        <v>131051498</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>91816</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9626,19 +9622,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051512</v>
+        <v>131051513</v>
       </c>
       <c r="B89" t="n">
-        <v>91814</v>
+        <v>92114</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468093</v>
+        <v>468342</v>
       </c>
       <c r="R89" t="n">
-        <v>7017305</v>
+        <v>7017232</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051513</v>
+        <v>131051512</v>
       </c>
       <c r="B90" t="n">
-        <v>92112</v>
+        <v>91816</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468342</v>
+        <v>468093</v>
       </c>
       <c r="R90" t="n">
-        <v>7017232</v>
+        <v>7017305</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -4957,7 +4957,7 @@
         <v>131031661</v>
       </c>
       <c r="B42" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>131031743</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030403</v>
+        <v>131031771</v>
       </c>
       <c r="B45" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,39 +5315,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468347</v>
+        <v>468053</v>
       </c>
       <c r="R45" t="n">
-        <v>7017234</v>
+        <v>7017383</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5379,7 +5374,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5389,12 +5384,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5421,10 +5411,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030207</v>
+        <v>131030403</v>
       </c>
       <c r="B46" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5461,13 +5451,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468282</v>
+        <v>468347</v>
       </c>
       <c r="R46" t="n">
-        <v>7017338</v>
+        <v>7017234</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5496,7 +5486,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5506,12 +5496,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,10 +5528,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030656</v>
+        <v>131030207</v>
       </c>
       <c r="B47" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5569,7 +5559,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5578,13 +5568,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468332</v>
+        <v>468282</v>
       </c>
       <c r="R47" t="n">
-        <v>7017164</v>
+        <v>7017338</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5613,7 +5603,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5623,12 +5613,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5655,10 +5645,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131031771</v>
+        <v>131030656</v>
       </c>
       <c r="B48" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,34 +5656,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468053</v>
+        <v>468332</v>
       </c>
       <c r="R48" t="n">
-        <v>7017383</v>
+        <v>7017164</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5725,7 +5720,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5735,7 +5730,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131030164</v>
+        <v>131031626</v>
       </c>
       <c r="B49" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5773,34 +5773,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468269</v>
+        <v>468198</v>
       </c>
       <c r="R49" t="n">
-        <v>7017349</v>
+        <v>7017261</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5832,7 +5837,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5842,7 +5847,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5869,10 +5879,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131031626</v>
+        <v>131030164</v>
       </c>
       <c r="B50" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5880,39 +5890,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468198</v>
+        <v>468269</v>
       </c>
       <c r="R50" t="n">
-        <v>7017261</v>
+        <v>7017349</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5944,7 +5949,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5954,12 +5959,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5989,7 +5989,7 @@
         <v>131030316</v>
       </c>
       <c r="B51" t="n">
-        <v>80382</v>
+        <v>80383</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>131030066</v>
       </c>
       <c r="B52" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>131030182</v>
       </c>
       <c r="B53" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>131030305</v>
       </c>
       <c r="B54" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>131031769</v>
       </c>
       <c r="B55" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>131031498</v>
       </c>
       <c r="B56" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131030174</v>
+        <v>131030313</v>
       </c>
       <c r="B57" t="n">
-        <v>58045</v>
+        <v>80354</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6680,42 +6680,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468273</v>
+        <v>468321</v>
       </c>
       <c r="R57" t="n">
-        <v>7017348</v>
+        <v>7017305</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6744,7 +6739,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6754,7 +6749,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6781,10 +6776,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131029927</v>
+        <v>131030174</v>
       </c>
       <c r="B58" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6809,11 +6804,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
           <t>lockläte, övriga läten</t>
@@ -6821,14 +6812,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468509</v>
+        <v>468273</v>
       </c>
       <c r="R58" t="n">
-        <v>7017474</v>
+        <v>7017348</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6860,7 +6851,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6870,7 +6861,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6897,10 +6888,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131030313</v>
+        <v>131029927</v>
       </c>
       <c r="B59" t="n">
-        <v>80353</v>
+        <v>58046</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6908,37 +6899,46 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468321</v>
+        <v>468509</v>
       </c>
       <c r="R59" t="n">
-        <v>7017305</v>
+        <v>7017474</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7007,7 +7007,7 @@
         <v>131030168</v>
       </c>
       <c r="B60" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7111,10 +7111,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031735</v>
+        <v>131031575</v>
       </c>
       <c r="B61" t="n">
-        <v>91812</v>
+        <v>80354</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,21 +7122,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468074</v>
+        <v>468209</v>
       </c>
       <c r="R61" t="n">
-        <v>7017313</v>
+        <v>7017210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7191,7 +7191,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7218,10 +7223,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031575</v>
+        <v>131031735</v>
       </c>
       <c r="B62" t="n">
-        <v>80353</v>
+        <v>91813</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7229,21 +7234,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7253,10 +7258,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468209</v>
+        <v>468074</v>
       </c>
       <c r="R62" t="n">
-        <v>7017210</v>
+        <v>7017313</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7288,7 +7293,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7298,12 +7303,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7333,7 +7333,7 @@
         <v>131031510</v>
       </c>
       <c r="B63" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>131035155</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>131030429</v>
       </c>
       <c r="B65" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B66" t="n">
-        <v>91812</v>
+        <v>79249</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R66" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B67" t="n">
-        <v>79248</v>
+        <v>91813</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R67" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>131051506</v>
       </c>
       <c r="B68" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051508</v>
+        <v>131051494</v>
       </c>
       <c r="B70" t="n">
-        <v>92114</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468291</v>
+        <v>468190</v>
       </c>
       <c r="R70" t="n">
-        <v>7017134</v>
+        <v>7017343</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B71" t="n">
-        <v>79248</v>
+        <v>92115</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R71" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,10 +8237,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B72" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R72" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8337,7 +8337,7 @@
         <v>131051490</v>
       </c>
       <c r="B73" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>131051491</v>
       </c>
       <c r="B78" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>131051483</v>
       </c>
       <c r="B79" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9028,10 +9028,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051492</v>
+        <v>131051482</v>
       </c>
       <c r="B80" t="n">
-        <v>79248</v>
+        <v>91813</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,21 +9039,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468247</v>
+        <v>468092</v>
       </c>
       <c r="R80" t="n">
-        <v>7017186</v>
+        <v>7017317</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9125,10 +9125,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051482</v>
+        <v>131051492</v>
       </c>
       <c r="B81" t="n">
-        <v>91812</v>
+        <v>79249</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9136,21 +9136,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9160,10 +9160,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468092</v>
+        <v>468247</v>
       </c>
       <c r="R81" t="n">
-        <v>7017317</v>
+        <v>7017186</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9222,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051489</v>
+        <v>131051496</v>
       </c>
       <c r="B82" t="n">
-        <v>79248</v>
+        <v>91817</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468318</v>
+        <v>468306</v>
       </c>
       <c r="R82" t="n">
-        <v>7017322</v>
+        <v>7017299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9293,11 +9293,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9324,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051496</v>
+        <v>131051489</v>
       </c>
       <c r="B83" t="n">
-        <v>91816</v>
+        <v>79249</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9335,21 +9330,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9359,10 +9354,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468306</v>
+        <v>468318</v>
       </c>
       <c r="R83" t="n">
-        <v>7017299</v>
+        <v>7017322</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9395,6 +9390,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9424,7 +9424,7 @@
         <v>131051497</v>
       </c>
       <c r="B84" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9514,10 +9514,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051486</v>
+        <v>131051498</v>
       </c>
       <c r="B85" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9549,10 +9549,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R85" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,10 +9611,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B86" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R86" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9711,7 +9711,7 @@
         <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051513</v>
+        <v>131051512</v>
       </c>
       <c r="B89" t="n">
-        <v>92114</v>
+        <v>91817</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468342</v>
+        <v>468093</v>
       </c>
       <c r="R89" t="n">
-        <v>7017232</v>
+        <v>7017305</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051512</v>
+        <v>131051513</v>
       </c>
       <c r="B90" t="n">
-        <v>91816</v>
+        <v>92115</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468093</v>
+        <v>468342</v>
       </c>
       <c r="R90" t="n">
-        <v>7017305</v>
+        <v>7017232</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5304,10 +5304,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131031771</v>
+        <v>131030403</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>57887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,34 +5315,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468053</v>
+        <v>468347</v>
       </c>
       <c r="R45" t="n">
-        <v>7017383</v>
+        <v>7017234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,7 +5379,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5384,7 +5389,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5411,7 +5421,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030403</v>
+        <v>131030207</v>
       </c>
       <c r="B46" t="n">
         <v>57887</v>
@@ -5451,13 +5461,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468347</v>
+        <v>468282</v>
       </c>
       <c r="R46" t="n">
-        <v>7017234</v>
+        <v>7017338</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5486,7 +5496,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5496,12 +5506,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Barkfläkta granar i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5538,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030207</v>
+        <v>131030656</v>
       </c>
       <c r="B47" t="n">
         <v>57887</v>
@@ -5559,7 +5569,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5568,13 +5578,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468282</v>
+        <v>468332</v>
       </c>
       <c r="R47" t="n">
-        <v>7017338</v>
+        <v>7017164</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5603,7 +5613,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5613,12 +5623,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5645,10 +5655,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131030656</v>
+        <v>131031771</v>
       </c>
       <c r="B48" t="n">
-        <v>57887</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5656,39 +5666,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468332</v>
+        <v>468053</v>
       </c>
       <c r="R48" t="n">
-        <v>7017164</v>
+        <v>7017383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5720,7 +5725,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5730,12 +5735,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,10 +5762,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131031626</v>
+        <v>131030164</v>
       </c>
       <c r="B49" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5773,39 +5773,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468198</v>
+        <v>468269</v>
       </c>
       <c r="R49" t="n">
-        <v>7017261</v>
+        <v>7017349</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5837,7 +5832,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5847,12 +5842,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5879,10 +5869,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131030164</v>
+        <v>131031626</v>
       </c>
       <c r="B50" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5890,34 +5880,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468269</v>
+        <v>468198</v>
       </c>
       <c r="R50" t="n">
-        <v>7017349</v>
+        <v>7017261</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5949,7 +5944,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5959,7 +5954,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6541,10 +6541,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131031498</v>
+        <v>131030313</v>
       </c>
       <c r="B56" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,53 +6552,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468224</v>
+        <v>468321</v>
       </c>
       <c r="R56" t="n">
-        <v>7017146</v>
+        <v>7017305</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6627,7 +6611,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6637,12 +6621,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6669,10 +6648,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131030313</v>
+        <v>131031498</v>
       </c>
       <c r="B57" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6680,37 +6659,53 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468321</v>
+        <v>468224</v>
       </c>
       <c r="R57" t="n">
-        <v>7017305</v>
+        <v>7017146</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6739,7 +6734,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6749,7 +6744,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051494</v>
+        <v>131051508</v>
       </c>
       <c r="B70" t="n">
-        <v>79249</v>
+        <v>92115</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468190</v>
+        <v>468291</v>
       </c>
       <c r="R70" t="n">
-        <v>7017343</v>
+        <v>7017134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051508</v>
+        <v>131051511</v>
       </c>
       <c r="B71" t="n">
-        <v>92115</v>
+        <v>79249</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,21 +8151,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468291</v>
+        <v>468075</v>
       </c>
       <c r="R71" t="n">
-        <v>7017134</v>
+        <v>7017357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051511</v>
+        <v>131051494</v>
       </c>
       <c r="B72" t="n">
         <v>79249</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468075</v>
+        <v>468190</v>
       </c>
       <c r="R72" t="n">
-        <v>7017357</v>
+        <v>7017343</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051497</v>
+        <v>131051498</v>
       </c>
       <c r="B84" t="n">
-        <v>91837</v>
+        <v>91817</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,19 +9432,23 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9514,7 +9518,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051498</v>
+        <v>131051486</v>
       </c>
       <c r="B85" t="n">
         <v>91817</v>
@@ -9549,10 +9553,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R85" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9611,10 +9615,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051486</v>
+        <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91817</v>
+        <v>91837</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9622,23 +9626,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R86" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051508</v>
+        <v>131051511</v>
       </c>
       <c r="B70" t="n">
-        <v>92115</v>
+        <v>79249</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468291</v>
+        <v>468075</v>
       </c>
       <c r="R70" t="n">
-        <v>7017134</v>
+        <v>7017357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,7 +8140,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051511</v>
+        <v>131051494</v>
       </c>
       <c r="B71" t="n">
         <v>79249</v>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468075</v>
+        <v>468190</v>
       </c>
       <c r="R71" t="n">
-        <v>7017357</v>
+        <v>7017343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,7 +8237,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051494</v>
+        <v>131051490</v>
       </c>
       <c r="B72" t="n">
         <v>79249</v>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468190</v>
+        <v>468271</v>
       </c>
       <c r="R72" t="n">
-        <v>7017343</v>
+        <v>7017382</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,6 +8308,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8334,10 +8339,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051490</v>
+        <v>131051508</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>92115</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8345,21 +8350,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8369,10 +8374,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468271</v>
+        <v>468291</v>
       </c>
       <c r="R73" t="n">
-        <v>7017382</v>
+        <v>7017134</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8405,11 +8410,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8824,10 +8824,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131051491</v>
+        <v>131051483</v>
       </c>
       <c r="B78" t="n">
-        <v>57887</v>
+        <v>80354</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,39 +8835,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468383</v>
+        <v>468300</v>
       </c>
       <c r="R78" t="n">
-        <v>7017207</v>
+        <v>7017272</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8900,11 +8895,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8931,10 +8921,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131051483</v>
+        <v>131051491</v>
       </c>
       <c r="B79" t="n">
-        <v>80354</v>
+        <v>57887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8942,34 +8932,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468300</v>
+        <v>468383</v>
       </c>
       <c r="R79" t="n">
-        <v>7017272</v>
+        <v>7017207</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9002,6 +8997,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9222,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051496</v>
+        <v>131051489</v>
       </c>
       <c r="B82" t="n">
-        <v>91817</v>
+        <v>79249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468306</v>
+        <v>468318</v>
       </c>
       <c r="R82" t="n">
-        <v>7017299</v>
+        <v>7017322</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9293,6 +9293,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9324,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051489</v>
+        <v>131051496</v>
       </c>
       <c r="B83" t="n">
-        <v>79249</v>
+        <v>91817</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9330,21 +9335,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9354,10 +9359,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468318</v>
+        <v>468306</v>
       </c>
       <c r="R83" t="n">
-        <v>7017322</v>
+        <v>7017299</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9390,11 +9395,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051498</v>
+        <v>131051497</v>
       </c>
       <c r="B84" t="n">
-        <v>91817</v>
+        <v>91837</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,23 +9432,19 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9518,7 +9514,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051486</v>
+        <v>131051498</v>
       </c>
       <c r="B85" t="n">
         <v>91817</v>
@@ -9553,10 +9549,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R85" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9615,10 +9611,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051497</v>
+        <v>131051486</v>
       </c>
       <c r="B86" t="n">
-        <v>91837</v>
+        <v>91817</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9626,19 +9622,23 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R86" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -7655,10 +7655,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051504</v>
+        <v>131051493</v>
       </c>
       <c r="B66" t="n">
-        <v>79249</v>
+        <v>91814</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,21 +7666,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7690,10 +7690,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468300</v>
+        <v>468072</v>
       </c>
       <c r="R66" t="n">
-        <v>7017272</v>
+        <v>7017314</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7752,10 +7752,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051493</v>
+        <v>131051504</v>
       </c>
       <c r="B67" t="n">
-        <v>91813</v>
+        <v>79250</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,21 +7763,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7787,10 +7787,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468072</v>
+        <v>468300</v>
       </c>
       <c r="R67" t="n">
-        <v>7017314</v>
+        <v>7017272</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7852,7 +7852,7 @@
         <v>131051506</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>131051507</v>
       </c>
       <c r="B69" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8043,10 +8043,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051511</v>
+        <v>131051508</v>
       </c>
       <c r="B70" t="n">
-        <v>79249</v>
+        <v>92116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,21 +8054,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8078,10 +8078,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468075</v>
+        <v>468291</v>
       </c>
       <c r="R70" t="n">
-        <v>7017357</v>
+        <v>7017134</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8140,10 +8140,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051494</v>
+        <v>131051511</v>
       </c>
       <c r="B71" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8175,10 +8175,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468190</v>
+        <v>468075</v>
       </c>
       <c r="R71" t="n">
-        <v>7017343</v>
+        <v>7017357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8237,10 +8237,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051490</v>
+        <v>131051494</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8272,10 +8272,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468271</v>
+        <v>468190</v>
       </c>
       <c r="R72" t="n">
-        <v>7017382</v>
+        <v>7017343</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8308,11 +8308,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8339,10 +8334,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051508</v>
+        <v>131051490</v>
       </c>
       <c r="B73" t="n">
-        <v>92115</v>
+        <v>79250</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8350,21 +8345,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8374,10 +8369,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468291</v>
+        <v>468271</v>
       </c>
       <c r="R73" t="n">
-        <v>7017134</v>
+        <v>7017382</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8410,6 +8405,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8439,7 +8439,7 @@
         <v>131051514</v>
       </c>
       <c r="B74" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>131051501</v>
       </c>
       <c r="B75" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8633,7 +8633,7 @@
         <v>131051487</v>
       </c>
       <c r="B76" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>131051481</v>
       </c>
       <c r="B77" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>131051483</v>
       </c>
       <c r="B78" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>131051491</v>
       </c>
       <c r="B79" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         <v>131051482</v>
       </c>
       <c r="B80" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>131051492</v>
       </c>
       <c r="B81" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9222,10 +9222,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051489</v>
+        <v>131051496</v>
       </c>
       <c r="B82" t="n">
-        <v>79249</v>
+        <v>91818</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,10 +9257,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468318</v>
+        <v>468306</v>
       </c>
       <c r="R82" t="n">
-        <v>7017322</v>
+        <v>7017299</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9293,11 +9293,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9324,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051496</v>
+        <v>131051489</v>
       </c>
       <c r="B83" t="n">
-        <v>91817</v>
+        <v>79250</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9335,21 +9330,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9359,10 +9354,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468306</v>
+        <v>468318</v>
       </c>
       <c r="R83" t="n">
-        <v>7017299</v>
+        <v>7017322</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9395,6 +9390,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051497</v>
+        <v>131051486</v>
       </c>
       <c r="B84" t="n">
-        <v>91837</v>
+        <v>91818</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,19 +9432,23 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9452,10 +9456,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468258</v>
+        <v>468362</v>
       </c>
       <c r="R84" t="n">
-        <v>7017130</v>
+        <v>7017236</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9517,7 +9521,7 @@
         <v>131051498</v>
       </c>
       <c r="B85" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9611,10 +9615,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051486</v>
+        <v>131051497</v>
       </c>
       <c r="B86" t="n">
-        <v>91817</v>
+        <v>91838</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9622,23 +9626,19 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9646,10 +9646,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468362</v>
+        <v>468258</v>
       </c>
       <c r="R86" t="n">
-        <v>7017236</v>
+        <v>7017130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9711,7 +9711,7 @@
         <v>131051503</v>
       </c>
       <c r="B87" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9808,7 +9808,7 @@
         <v>131051495</v>
       </c>
       <c r="B88" t="n">
-        <v>80354</v>
+        <v>80355</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9902,10 +9902,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051512</v>
+        <v>131051513</v>
       </c>
       <c r="B89" t="n">
-        <v>91817</v>
+        <v>92116</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9913,21 +9913,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9937,10 +9937,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468093</v>
+        <v>468342</v>
       </c>
       <c r="R89" t="n">
-        <v>7017305</v>
+        <v>7017232</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9999,10 +9999,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051513</v>
+        <v>131051512</v>
       </c>
       <c r="B90" t="n">
-        <v>92115</v>
+        <v>91818</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10010,21 +10010,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10034,10 +10034,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468342</v>
+        <v>468093</v>
       </c>
       <c r="R90" t="n">
-        <v>7017232</v>
+        <v>7017305</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10099,7 +10099,7 @@
         <v>131051502</v>
       </c>
       <c r="B91" t="n">
-        <v>91817</v>
+        <v>91818</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>131051488</v>
       </c>
       <c r="B92" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57887</v>
+        <v>57896</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57896</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -5181,7 +5181,7 @@
         <v>131029902</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120089765</v>
+        <v>131051508</v>
       </c>
       <c r="B2" t="n">
-        <v>77474</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häste, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468082</v>
+        <v>468291</v>
       </c>
       <c r="R2" t="n">
-        <v>7016955</v>
+        <v>7017134</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120089732</v>
+        <v>131051513</v>
       </c>
       <c r="B3" t="n">
-        <v>79131</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Häste, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468082</v>
+        <v>468342</v>
       </c>
       <c r="R3" t="n">
-        <v>7016955</v>
+        <v>7017232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,55 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120089741</v>
+        <v>130865266</v>
       </c>
       <c r="B4" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Häste, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468090</v>
+        <v>468470</v>
       </c>
       <c r="R4" t="n">
-        <v>7016961</v>
+        <v>7017481</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-27</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129216621</v>
+        <v>131004202</v>
       </c>
       <c r="B5" t="n">
-        <v>78078</v>
+        <v>91905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +987,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468111</v>
+        <v>468431</v>
       </c>
       <c r="R5" t="n">
-        <v>7016957</v>
+        <v>7017499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1041,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129216628</v>
+        <v>131031735</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>91905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,34 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468004</v>
+        <v>468074</v>
       </c>
       <c r="R6" t="n">
-        <v>7016903</v>
+        <v>7017313</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,12 +1148,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1178,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129216626</v>
+        <v>131051482</v>
       </c>
       <c r="B7" t="n">
-        <v>80175</v>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468064</v>
+        <v>468092</v>
       </c>
       <c r="R7" t="n">
-        <v>7016921</v>
+        <v>7017317</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129216620</v>
+        <v>131051493</v>
       </c>
       <c r="B8" t="n">
-        <v>79660</v>
+        <v>91905</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468111</v>
+        <v>468072</v>
       </c>
       <c r="R8" t="n">
-        <v>7016957</v>
+        <v>7017314</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,12 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1374,10 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129216625</v>
+        <v>131051499</v>
       </c>
       <c r="B9" t="n">
-        <v>80175</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1395,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468082</v>
+        <v>468038</v>
       </c>
       <c r="R9" t="n">
-        <v>7016924</v>
+        <v>7017261</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,12 +1449,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,45 +1481,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129216619</v>
+        <v>130865182</v>
       </c>
       <c r="B10" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468080</v>
+        <v>468493</v>
       </c>
       <c r="R10" t="n">
-        <v>7016970</v>
+        <v>7017468</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,12 +1546,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,22 +1576,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129216615</v>
+        <v>131014503</v>
       </c>
       <c r="B11" t="n">
-        <v>78078</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1579,37 +1599,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468083</v>
+        <v>468269</v>
       </c>
       <c r="R11" t="n">
-        <v>7016953</v>
+        <v>7017408</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,12 +1653,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1653,22 +1683,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129216618</v>
+        <v>131030164</v>
       </c>
       <c r="B12" t="n">
-        <v>57890</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1676,42 +1706,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468030</v>
+        <v>468269</v>
       </c>
       <c r="R12" t="n">
-        <v>7016977</v>
+        <v>7017349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,12 +1760,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1758,22 +1790,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129216614</v>
+        <v>131031769</v>
       </c>
       <c r="B13" t="n">
-        <v>79660</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1781,34 +1813,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468083</v>
+        <v>468053</v>
       </c>
       <c r="R13" t="n">
-        <v>7016953</v>
+        <v>7017379</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1835,12 +1867,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1855,57 +1897,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129216623</v>
+        <v>131051486</v>
       </c>
       <c r="B14" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468101</v>
+        <v>468362</v>
       </c>
       <c r="R14" t="n">
-        <v>7016933</v>
+        <v>7017236</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1932,12 +1974,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,10 +2006,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129216627</v>
+        <v>131051496</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,34 +2017,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468021</v>
+        <v>468306</v>
       </c>
       <c r="R15" t="n">
-        <v>7016907</v>
+        <v>7017299</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2029,12 +2071,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2061,45 +2103,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129216617</v>
+        <v>131051498</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>468082</v>
+        <v>468258</v>
       </c>
       <c r="R16" t="n">
-        <v>7016961</v>
+        <v>7017130</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2126,12 +2168,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,50 +2200,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129216624</v>
+        <v>131051501</v>
       </c>
       <c r="B17" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468088</v>
+        <v>468359</v>
       </c>
       <c r="R17" t="n">
-        <v>7016934</v>
+        <v>7017199</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2228,17 +2265,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>En blommande stängel och flera fjolårsstänglar.</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,10 +2297,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129216611</v>
+        <v>131051502</v>
       </c>
       <c r="B18" t="n">
-        <v>79070</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2276,34 +2308,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>468037</v>
+        <v>468342</v>
       </c>
       <c r="R18" t="n">
-        <v>7016963</v>
+        <v>7017231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2330,12 +2362,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,45 +2394,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129216612</v>
+        <v>131051507</v>
       </c>
       <c r="B19" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>468060</v>
+        <v>468247</v>
       </c>
       <c r="R19" t="n">
-        <v>7016981</v>
+        <v>7017164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2427,12 +2459,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2459,45 +2491,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129216622</v>
+        <v>131051512</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>468103</v>
+        <v>468093</v>
       </c>
       <c r="R20" t="n">
-        <v>7016954</v>
+        <v>7017305</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2524,12 +2556,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2556,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129216613</v>
+        <v>131051514</v>
       </c>
       <c r="B21" t="n">
-        <v>79070</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,34 +2599,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stenbrännorna, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468083</v>
+        <v>468097</v>
       </c>
       <c r="R21" t="n">
-        <v>7016953</v>
+        <v>7017318</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2621,12 +2653,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2653,53 +2685,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130865454</v>
+        <v>129216611</v>
       </c>
       <c r="B22" t="n">
-        <v>58043</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>468469</v>
+        <v>468037</v>
       </c>
       <c r="R22" t="n">
-        <v>7017487</v>
+        <v>7016963</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2723,22 +2750,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:38</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2753,57 +2770,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130865266</v>
+        <v>129216613</v>
       </c>
       <c r="B23" t="n">
-        <v>91805</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>468470</v>
+        <v>468083</v>
       </c>
       <c r="R23" t="n">
-        <v>7017481</v>
+        <v>7016953</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2830,22 +2847,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2860,62 +2867,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130865254</v>
+        <v>129216628</v>
       </c>
       <c r="B24" t="n">
-        <v>57881</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468479</v>
+        <v>468004</v>
       </c>
       <c r="R24" t="n">
-        <v>7017488</v>
+        <v>7016903</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2942,27 +2944,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:19</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Bearbetad grov död gran</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2977,57 +2964,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130865182</v>
+        <v>129216631</v>
       </c>
       <c r="B25" t="n">
-        <v>91809</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>468493</v>
+        <v>467949</v>
       </c>
       <c r="R25" t="n">
-        <v>7017468</v>
+        <v>7016865</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3054,22 +3041,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,65 +3061,60 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130865004</v>
+        <v>130865481</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>468518</v>
+        <v>468481</v>
       </c>
       <c r="R26" t="n">
-        <v>7017522</v>
+        <v>7017551</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3171,7 +3143,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3181,12 +3153,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,30 +3180,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130865357</v>
+        <v>131030066</v>
       </c>
       <c r="B27" t="n">
-        <v>91829</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3244,13 +3215,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468423</v>
+        <v>468316</v>
       </c>
       <c r="R27" t="n">
-        <v>7017415</v>
+        <v>7017340</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3274,22 +3245,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,50 +3287,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130865432</v>
+        <v>131030168</v>
       </c>
       <c r="B28" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>468444</v>
+        <v>468272</v>
       </c>
       <c r="R28" t="n">
-        <v>7017417</v>
+        <v>7017348</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3386,27 +3352,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:33</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3433,59 +3394,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130865409</v>
+        <v>131030331</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>468505</v>
+        <v>468338</v>
       </c>
       <c r="R29" t="n">
-        <v>7017445</v>
+        <v>7017310</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3512,27 +3459,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bearbetade död gran. Gott om spår av födosök i området.</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3559,50 +3501,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130865230</v>
+        <v>131030429</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>468478</v>
+        <v>468347</v>
       </c>
       <c r="R30" t="n">
-        <v>7017505</v>
+        <v>7017228</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3629,27 +3566,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3676,50 +3608,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130864922</v>
+        <v>131031743</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>468571</v>
+        <v>468070</v>
       </c>
       <c r="R31" t="n">
-        <v>7017501</v>
+        <v>7017311</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3746,27 +3673,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:54</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Bearbetad gran med typiska rand mönster.</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3793,57 +3715,48 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130865014</v>
+        <v>131031771</v>
       </c>
       <c r="B32" t="n">
-        <v>58043</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468521</v>
+        <v>468053</v>
       </c>
       <c r="R32" t="n">
-        <v>7017519</v>
+        <v>7017383</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3867,22 +3780,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3909,14 +3822,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130865481</v>
+        <v>131051481</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3940,17 +3853,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>468481</v>
+        <v>468333</v>
       </c>
       <c r="R33" t="n">
-        <v>7017551</v>
+        <v>7017253</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3974,22 +3887,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-01-25</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4004,66 +3907,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131004176</v>
+        <v>131051489</v>
       </c>
       <c r="B34" t="n">
-        <v>58045</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>468504</v>
+        <v>468318</v>
       </c>
       <c r="R34" t="n">
-        <v>7017482</v>
+        <v>7017322</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4090,22 +3984,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Smal bål 0,5 m lång</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4120,60 +4009,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131014503</v>
+        <v>131051490</v>
       </c>
       <c r="B35" t="n">
-        <v>91816</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>468269</v>
+        <v>468271</v>
       </c>
       <c r="R35" t="n">
-        <v>7017408</v>
+        <v>7017382</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4197,22 +4086,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>bål 0,4 m lång</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4227,66 +4111,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131006989</v>
+        <v>131051492</v>
       </c>
       <c r="B36" t="n">
-        <v>58045</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>468239</v>
+        <v>468247</v>
       </c>
       <c r="R36" t="n">
-        <v>7017405</v>
+        <v>7017186</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4313,22 +4188,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,66 +4208,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131007096</v>
+        <v>131051494</v>
       </c>
       <c r="B37" t="n">
-        <v>57883</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>468248</v>
+        <v>468190</v>
       </c>
       <c r="R37" t="n">
-        <v>7017412</v>
+        <v>7017343</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4429,27 +4285,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Landade kort på tall och hackade innan den upptäckte mig.</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4464,76 +4305,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131008392</v>
+        <v>131051503</v>
       </c>
       <c r="B38" t="n">
-        <v>57886</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>468482</v>
+        <v>468303</v>
       </c>
       <c r="R38" t="n">
-        <v>7017550</v>
+        <v>7017139</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4557,27 +4382,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:17</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bearbetning av större gran.</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4592,60 +4402,60 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131005337</v>
+        <v>131051504</v>
       </c>
       <c r="B39" t="n">
-        <v>79005</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>468253</v>
+        <v>468300</v>
       </c>
       <c r="R39" t="n">
-        <v>7017439</v>
+        <v>7017272</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4669,22 +4479,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4699,71 +4499,57 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131004190</v>
+        <v>131051506</v>
       </c>
       <c r="B40" t="n">
-        <v>57886</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>468504</v>
+        <v>468096</v>
       </c>
       <c r="R40" t="n">
-        <v>7017482</v>
+        <v>7017318</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4790,27 +4576,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>12:01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Samma träd som den bearbetade vid senaste besöket.</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4825,62 +4596,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131007087</v>
+        <v>131051511</v>
       </c>
       <c r="B41" t="n">
-        <v>57886</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>468239</v>
+        <v>468075</v>
       </c>
       <c r="R41" t="n">
-        <v>7017405</v>
+        <v>7017357</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4907,27 +4673,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:36</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Barkfläk</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4942,22 +4693,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131031661</v>
+        <v>131005337</v>
       </c>
       <c r="B42" t="n">
-        <v>57887</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4965,42 +4716,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>468161</v>
+        <v>468253</v>
       </c>
       <c r="R42" t="n">
-        <v>7017332</v>
+        <v>7017439</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5024,27 +4770,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:32</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Klena barkfläkta granar i området</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5071,10 +4812,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131031743</v>
+        <v>128139048</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5082,34 +4823,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>468070</v>
+        <v>468103</v>
       </c>
       <c r="R43" t="n">
-        <v>7017311</v>
+        <v>7016895</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,22 +4877,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>14:44</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5166,22 +4897,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131029902</v>
+        <v>129216625</v>
       </c>
       <c r="B44" t="n">
-        <v>57948</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5189,48 +4920,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>468507</v>
+        <v>468082</v>
       </c>
       <c r="R44" t="n">
-        <v>7017469</v>
+        <v>7016924</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5257,27 +4974,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5292,22 +4994,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131030403</v>
+        <v>129216626</v>
       </c>
       <c r="B45" t="n">
-        <v>57887</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5315,39 +5017,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>468347</v>
+        <v>468064</v>
       </c>
       <c r="R45" t="n">
-        <v>7017234</v>
+        <v>7016921</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5374,27 +5071,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Barkfläkta granar i området</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5409,22 +5091,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131030207</v>
+        <v>129216627</v>
       </c>
       <c r="B46" t="n">
-        <v>57887</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5432,42 +5114,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>468282</v>
+        <v>468021</v>
       </c>
       <c r="R46" t="n">
-        <v>7017338</v>
+        <v>7016907</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5491,27 +5168,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>13:33</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5526,22 +5188,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131030656</v>
+        <v>129216630</v>
       </c>
       <c r="B47" t="n">
-        <v>57887</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5549,39 +5211,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>468332</v>
+        <v>467952</v>
       </c>
       <c r="R47" t="n">
-        <v>7017164</v>
+        <v>7016864</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5608,27 +5265,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>13:59</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gott om barkfläkta granar i området</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5643,22 +5285,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131031771</v>
+        <v>131030313</v>
       </c>
       <c r="B48" t="n">
-        <v>79249</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5666,21 +5308,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5690,13 +5332,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>468053</v>
+        <v>468321</v>
       </c>
       <c r="R48" t="n">
-        <v>7017383</v>
+        <v>7017305</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5725,7 +5367,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5735,7 +5377,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5762,10 +5404,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131030164</v>
+        <v>131031575</v>
       </c>
       <c r="B49" t="n">
-        <v>91817</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5773,21 +5415,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5797,10 +5439,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>468269</v>
+        <v>468209</v>
       </c>
       <c r="R49" t="n">
-        <v>7017349</v>
+        <v>7017210</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5832,7 +5474,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5842,7 +5484,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5869,10 +5516,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131031626</v>
+        <v>131051483</v>
       </c>
       <c r="B50" t="n">
-        <v>57887</v>
+        <v>80432</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5880,39 +5527,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>468198</v>
+        <v>468300</v>
       </c>
       <c r="R50" t="n">
-        <v>7017261</v>
+        <v>7017272</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5939,27 +5581,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>14:28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5974,57 +5601,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131030316</v>
+        <v>131051487</v>
       </c>
       <c r="B51" t="n">
-        <v>80383</v>
+        <v>80432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>468318</v>
+        <v>468320</v>
       </c>
       <c r="R51" t="n">
-        <v>7017304</v>
+        <v>7017296</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6051,22 +5678,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6081,22 +5698,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131030066</v>
+        <v>131051495</v>
       </c>
       <c r="B52" t="n">
-        <v>79249</v>
+        <v>80432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,34 +5721,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>468316</v>
+        <v>468306</v>
       </c>
       <c r="R52" t="n">
-        <v>7017340</v>
+        <v>7017299</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6158,22 +5775,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6188,65 +5795,60 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131030182</v>
+        <v>131030316</v>
       </c>
       <c r="B53" t="n">
-        <v>57887</v>
+        <v>80461</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>468272</v>
+        <v>468318</v>
       </c>
       <c r="R53" t="n">
-        <v>7017348</v>
+        <v>7017304</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6275,7 +5877,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6285,12 +5887,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Barkfläkt gran</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6317,10 +5914,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131030305</v>
+        <v>120089765</v>
       </c>
       <c r="B54" t="n">
-        <v>57887</v>
+        <v>78334</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6328,39 +5925,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Häste, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>468302</v>
+        <v>468082</v>
       </c>
       <c r="R54" t="n">
-        <v>7017297</v>
+        <v>7016955</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6387,27 +5979,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6422,22 +5999,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131031769</v>
+        <v>129216615</v>
       </c>
       <c r="B55" t="n">
-        <v>91817</v>
+        <v>78334</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6445,34 +6022,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>468053</v>
+        <v>468083</v>
       </c>
       <c r="R55" t="n">
-        <v>7017379</v>
+        <v>7016953</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6499,22 +6076,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:49</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6529,22 +6096,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131030313</v>
+        <v>129216621</v>
       </c>
       <c r="B56" t="n">
-        <v>80354</v>
+        <v>78334</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6552,37 +6119,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6487</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>468321</v>
+        <v>468111</v>
       </c>
       <c r="R56" t="n">
-        <v>7017305</v>
+        <v>7016957</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6606,22 +6173,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:39</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6636,39 +6193,39 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristofer Holmsten</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131031498</v>
+        <v>130865254</v>
       </c>
       <c r="B57" t="n">
-        <v>57887</v>
+        <v>57950</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6676,33 +6233,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>468224</v>
+        <v>468479</v>
       </c>
       <c r="R57" t="n">
-        <v>7017146</v>
+        <v>7017488</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6729,27 +6275,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
+          <t>Bearbetad grov död gran</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6776,50 +6322,50 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131030174</v>
+        <v>131004206</v>
       </c>
       <c r="B58" t="n">
-        <v>58046</v>
+        <v>57950</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>468273</v>
+        <v>468431</v>
       </c>
       <c r="R58" t="n">
-        <v>7017348</v>
+        <v>7017499</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6846,22 +6392,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6888,54 +6434,54 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131029927</v>
+        <v>131007096</v>
       </c>
       <c r="B59" t="n">
-        <v>58046</v>
+        <v>57950</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>468509</v>
+        <v>468248</v>
       </c>
       <c r="R59" t="n">
-        <v>7017474</v>
+        <v>7017412</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6962,22 +6508,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Landade kort på tall och hackade innan den upptäckte mig.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7004,48 +6555,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131030168</v>
+        <v>131035155</v>
       </c>
       <c r="B60" t="n">
-        <v>79249</v>
+        <v>57950</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>468272</v>
+        <v>468176</v>
       </c>
       <c r="R60" t="n">
-        <v>7017348</v>
+        <v>7017297</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7072,19 +6628,9 @@
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:29</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-02-04</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7111,10 +6657,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131031575</v>
+        <v>130864922</v>
       </c>
       <c r="B61" t="n">
-        <v>80354</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7122,34 +6668,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>468209</v>
+        <v>468571</v>
       </c>
       <c r="R61" t="n">
-        <v>7017210</v>
+        <v>7017501</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7176,27 +6727,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Bearbetad gran med typiska rand mönster.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7223,10 +6774,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131031735</v>
+        <v>130865004</v>
       </c>
       <c r="B62" t="n">
-        <v>91813</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7234,34 +6785,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>468074</v>
+        <v>468518</v>
       </c>
       <c r="R62" t="n">
-        <v>7017313</v>
+        <v>7017522</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7288,22 +6844,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7330,27 +6891,27 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131031510</v>
+        <v>130865230</v>
       </c>
       <c r="B63" t="n">
-        <v>58259</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7358,26 +6919,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>468222</v>
+        <v>468478</v>
       </c>
       <c r="R63" t="n">
-        <v>7017146</v>
+        <v>7017505</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7404,22 +6961,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7446,10 +7008,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131035155</v>
+        <v>130865409</v>
       </c>
       <c r="B64" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7457,16 +7019,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -7474,25 +7036,34 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr"/>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>468176</v>
+        <v>468505</v>
       </c>
       <c r="R64" t="n">
-        <v>7017297</v>
+        <v>7017445</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7516,12 +7087,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Bearbetade död gran. Gott om spår av födosök i området.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7548,10 +7134,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131030429</v>
+        <v>130865432</v>
       </c>
       <c r="B65" t="n">
-        <v>79249</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7559,34 +7145,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>468347</v>
+        <v>468444</v>
       </c>
       <c r="R65" t="n">
-        <v>7017228</v>
+        <v>7017417</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7613,22 +7204,27 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-01-25</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7655,10 +7251,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131051493</v>
+        <v>131004190</v>
       </c>
       <c r="B66" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7666,34 +7262,48 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>468072</v>
+        <v>468504</v>
       </c>
       <c r="R66" t="n">
-        <v>7017314</v>
+        <v>7017482</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7720,12 +7330,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Samma träd som den bearbetade vid senaste besöket.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7740,22 +7365,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131051504</v>
+        <v>131007087</v>
       </c>
       <c r="B67" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7763,34 +7388,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>468300</v>
+        <v>468239</v>
       </c>
       <c r="R67" t="n">
-        <v>7017272</v>
+        <v>7017405</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7817,12 +7447,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7837,22 +7482,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131051506</v>
+        <v>131008392</v>
       </c>
       <c r="B68" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7860,37 +7505,53 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>468096</v>
+        <v>468482</v>
       </c>
       <c r="R68" t="n">
-        <v>7017318</v>
+        <v>7017550</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7914,12 +7575,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Bearbetning av större gran.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7934,22 +7610,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131051507</v>
+        <v>131029902</v>
       </c>
       <c r="B69" t="n">
-        <v>91818</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7957,34 +7633,48 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>468247</v>
+        <v>468507</v>
       </c>
       <c r="R69" t="n">
-        <v>7017164</v>
+        <v>7017469</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8011,12 +7701,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>2+1. Födosök på samma gran. Mycket höga livsmiljövärden för tretå i närområdet. Tredje fågel flög bort.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8031,22 +7736,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131051508</v>
+        <v>131030182</v>
       </c>
       <c r="B70" t="n">
-        <v>92116</v>
+        <v>57953</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8054,37 +7759,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>468291</v>
+        <v>468272</v>
       </c>
       <c r="R70" t="n">
-        <v>7017134</v>
+        <v>7017348</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8108,12 +7818,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8128,22 +7853,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131051511</v>
+        <v>131030207</v>
       </c>
       <c r="B71" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8151,37 +7876,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>468075</v>
+        <v>468282</v>
       </c>
       <c r="R71" t="n">
-        <v>7017357</v>
+        <v>7017338</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8205,12 +7935,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8225,22 +7970,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131051494</v>
+        <v>131030305</v>
       </c>
       <c r="B72" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8248,34 +7993,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>468190</v>
+        <v>468302</v>
       </c>
       <c r="R72" t="n">
-        <v>7017343</v>
+        <v>7017297</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8302,12 +8052,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8322,22 +8087,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131051490</v>
+        <v>131030403</v>
       </c>
       <c r="B73" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8345,34 +8110,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>468271</v>
+        <v>468347</v>
       </c>
       <c r="R73" t="n">
-        <v>7017382</v>
+        <v>7017234</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8399,17 +8169,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>bål 0,4 m lång</t>
+          <t>Barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8424,22 +8204,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131051514</v>
+        <v>131030656</v>
       </c>
       <c r="B74" t="n">
-        <v>91818</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8447,34 +8227,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>468097</v>
+        <v>468332</v>
       </c>
       <c r="R74" t="n">
-        <v>7017318</v>
+        <v>7017164</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8501,12 +8286,27 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Gott om barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8521,22 +8321,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131051501</v>
+        <v>131031498</v>
       </c>
       <c r="B75" t="n">
-        <v>91818</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8544,34 +8344,50 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>468359</v>
+        <v>468224</v>
       </c>
       <c r="R75" t="n">
-        <v>7017199</v>
+        <v>7017146</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8598,12 +8414,27 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Bearbetade medelgrov gran. Flög över till klenare gran när jag närmade mig men förvånansvärt obrydd.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8618,22 +8449,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131051487</v>
+        <v>131031626</v>
       </c>
       <c r="B76" t="n">
-        <v>80355</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8641,34 +8472,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>468320</v>
+        <v>468198</v>
       </c>
       <c r="R76" t="n">
-        <v>7017296</v>
+        <v>7017261</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8695,12 +8531,27 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Barkfläkt gran</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8715,22 +8566,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131051481</v>
+        <v>131031661</v>
       </c>
       <c r="B77" t="n">
-        <v>79250</v>
+        <v>57953</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8738,34 +8589,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>468333</v>
+        <v>468161</v>
       </c>
       <c r="R77" t="n">
-        <v>7017253</v>
+        <v>7017332</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8792,12 +8648,27 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Klena barkfläkta granar i området</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8812,22 +8683,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131051483</v>
+        <v>131031700</v>
       </c>
       <c r="B78" t="n">
-        <v>80355</v>
+        <v>57953</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8835,34 +8706,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>468300</v>
+        <v>468109</v>
       </c>
       <c r="R78" t="n">
-        <v>7017272</v>
+        <v>7017329</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8889,12 +8765,27 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Flera barkfläkta granar i området.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8909,22 +8800,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131051491</v>
+        <v>131031722</v>
       </c>
       <c r="B79" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8957,17 +8848,17 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>468383</v>
+        <v>468105</v>
       </c>
       <c r="R79" t="n">
-        <v>7017207</v>
+        <v>7017297</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8991,17 +8882,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Med kådflöde.</t>
+          <t>Barkfläkta granar. Höga till mycket höga livsmiljövärden för tretåig hackspett i området.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9016,22 +8917,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131051482</v>
+        <v>131051491</v>
       </c>
       <c r="B80" t="n">
-        <v>91814</v>
+        <v>57953</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9039,34 +8940,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>468092</v>
+        <v>468383</v>
       </c>
       <c r="R80" t="n">
-        <v>7017317</v>
+        <v>7017207</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9099,6 +9005,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Med kådflöde.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9125,45 +9036,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131051492</v>
+        <v>131031510</v>
       </c>
       <c r="B81" t="n">
-        <v>79250</v>
+        <v>58327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>103015</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>468247</v>
+        <v>468222</v>
       </c>
       <c r="R81" t="n">
-        <v>7017186</v>
+        <v>7017146</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9190,12 +9110,22 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9210,22 +9140,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131051496</v>
+        <v>129216618</v>
       </c>
       <c r="B82" t="n">
-        <v>91818</v>
+        <v>58114</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9233,34 +9163,42 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>468306</v>
+        <v>468030</v>
       </c>
       <c r="R82" t="n">
-        <v>7017299</v>
+        <v>7016977</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9287,12 +9225,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9319,10 +9257,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131051489</v>
+        <v>130865014</v>
       </c>
       <c r="B83" t="n">
-        <v>79250</v>
+        <v>58114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9330,37 +9268,46 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>468318</v>
+        <v>468521</v>
       </c>
       <c r="R83" t="n">
-        <v>7017322</v>
+        <v>7017519</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9384,17 +9331,22 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Smal bål 0,5 m lång</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9409,22 +9361,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131051486</v>
+        <v>130865454</v>
       </c>
       <c r="B84" t="n">
-        <v>91818</v>
+        <v>58114</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9432,37 +9384,42 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>468362</v>
+        <v>468469</v>
       </c>
       <c r="R84" t="n">
-        <v>7017236</v>
+        <v>7017487</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9486,12 +9443,22 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9506,22 +9473,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131051498</v>
+        <v>131004176</v>
       </c>
       <c r="B85" t="n">
-        <v>91818</v>
+        <v>58114</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9529,34 +9496,43 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>468258</v>
+        <v>468504</v>
       </c>
       <c r="R85" t="n">
-        <v>7017130</v>
+        <v>7017482</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9583,12 +9559,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9603,22 +9589,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131051497</v>
+        <v>131006989</v>
       </c>
       <c r="B86" t="n">
-        <v>91838</v>
+        <v>58114</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9626,30 +9612,43 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>468258</v>
+        <v>468239</v>
       </c>
       <c r="R86" t="n">
-        <v>7017130</v>
+        <v>7017405</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9676,12 +9675,22 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9696,22 +9705,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131051503</v>
+        <v>131029927</v>
       </c>
       <c r="B87" t="n">
-        <v>79250</v>
+        <v>58114</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9719,34 +9728,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Stacktjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>468303</v>
+        <v>468509</v>
       </c>
       <c r="R87" t="n">
-        <v>7017139</v>
+        <v>7017474</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9773,12 +9791,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9793,22 +9821,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131051495</v>
+        <v>131030174</v>
       </c>
       <c r="B88" t="n">
-        <v>80355</v>
+        <v>58114</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9816,34 +9844,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stacktjärnen, Rödön, Stacktjärnen, Rödön, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>468306</v>
+        <v>468273</v>
       </c>
       <c r="R88" t="n">
-        <v>7017299</v>
+        <v>7017348</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9870,12 +9903,22 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9890,57 +9933,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Kristofer Holmsten</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131051513</v>
+        <v>128139051</v>
       </c>
       <c r="B89" t="n">
-        <v>92116</v>
+        <v>99120</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>658</v>
+        <v>219811</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>468342</v>
+        <v>468099</v>
       </c>
       <c r="R89" t="n">
-        <v>7017232</v>
+        <v>7016876</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9967,12 +10010,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9999,45 +10042,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131051512</v>
+        <v>120089741</v>
       </c>
       <c r="B90" t="n">
-        <v>91818</v>
+        <v>99118</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Häste, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>468093</v>
+        <v>468090</v>
       </c>
       <c r="R90" t="n">
-        <v>7017305</v>
+        <v>7016961</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10064,12 +10112,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10096,45 +10144,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131051502</v>
+        <v>129216612</v>
       </c>
       <c r="B91" t="n">
-        <v>91818</v>
+        <v>99118</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>468342</v>
+        <v>468060</v>
       </c>
       <c r="R91" t="n">
-        <v>7017231</v>
+        <v>7016981</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10161,12 +10209,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10193,41 +10241,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131051488</v>
+        <v>129216617</v>
       </c>
       <c r="B92" t="n">
-        <v>91838</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stacktjärnen, Jmt</t>
+          <t>Stenbrännorna, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>468309</v>
+        <v>468082</v>
       </c>
       <c r="R92" t="n">
-        <v>7017265</v>
+        <v>7016961</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10254,12 +10306,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10283,6 +10335,695 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129216619</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>468080</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7016970</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129216622</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>468103</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7016954</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129216623</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>468101</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7016933</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129216624</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>468088</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7016934</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>En blommande stängel och flera fjolårsstänglar.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120089732</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Häste, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>468082</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7016955</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-27</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129216614</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>468083</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7016953</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129216620</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stenbrännorna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>468111</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7016957</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Rödön</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3992-2026 artfynd.xlsx
+++ b/artfynd/A 3992-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051482</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051493</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031769</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051507</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051512</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051514</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1565,6 +1610,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216611</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216613</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216628</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216631</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031743</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031771</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051492</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2264,6 +2344,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051494</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2361,6 +2446,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051506</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2458,6 +2548,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051511</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2565,6 +2660,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131005337</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2662,6 +2762,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128139048</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2759,6 +2864,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216625</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2856,6 +2966,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216626</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2953,6 +3068,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216627</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3050,6 +3170,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216630</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3162,6 +3287,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031575</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3259,6 +3389,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120089765</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3356,6 +3491,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216615</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3453,6 +3593,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216621</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3574,6 +3719,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131007096</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3676,6 +3826,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131035155</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3793,6 +3948,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131007087</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3921,6 +4081,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031498</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031626</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4155,6 +4325,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031661</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4272,6 +4447,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031700</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4389,6 +4569,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031722</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4505,6 +4690,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131031510</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4610,6 +4800,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216618</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4726,6 +4921,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131006989</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4823,6 +5023,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128139051</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4925,6 +5130,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120089741</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5022,6 +5232,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216612</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5119,6 +5334,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216617</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5216,6 +5436,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216619</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5313,6 +5538,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216622</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5410,6 +5640,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216623</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5517,6 +5752,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216624</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5614,6 +5854,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120089732</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5711,6 +5956,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216614</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5808,6 +6058,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129216620</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5905,6 +6160,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051508</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6002,6 +6262,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051513</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6109,6 +6374,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865266</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6216,6 +6486,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131004202</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6323,6 +6598,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865182</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6430,6 +6710,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131014503</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6537,6 +6822,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030164</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6634,6 +6924,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051486</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6731,6 +7026,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051496</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6828,6 +7128,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051498</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6925,6 +7230,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051501</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7022,6 +7332,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051502</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7129,6 +7444,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865481</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7236,6 +7556,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030066</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7343,6 +7668,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030168</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7450,6 +7780,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030331</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7557,6 +7892,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030429</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7654,6 +7994,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051481</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7756,6 +8101,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051489</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7858,6 +8208,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051490</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7955,6 +8310,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051503</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8052,6 +8412,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051504</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8159,6 +8524,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030313</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8256,6 +8626,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051483</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8353,6 +8728,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051487</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8450,6 +8830,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051495</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8557,6 +8942,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030316</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8674,6 +9064,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865254</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8786,6 +9181,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131004206</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8903,6 +9303,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130864922</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9020,6 +9425,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865004</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9137,6 +9547,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865230</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9263,6 +9678,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865409</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9380,6 +9800,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865432</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9506,6 +9931,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131004190</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9634,6 +10064,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131008392</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9760,6 +10195,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131029902</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9877,6 +10317,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030182</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9994,6 +10439,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030207</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10111,6 +10561,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030305</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10228,6 +10683,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030403</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10345,6 +10805,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030656</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10452,6 +10917,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131051491</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10568,6 +11038,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865014</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10680,6 +11155,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130865454</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10796,6 +11276,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131004176</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10912,6 +11397,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131029927</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11024,8 +11514,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131030174</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>